--- a/testdata/listForExecution.xlsx
+++ b/testdata/listForExecution.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="990" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1092" uniqueCount="355">
   <si>
     <t>TestName</t>
   </si>
@@ -59,18 +59,18 @@
     <t>data</t>
   </si>
   <si>
+    <t>off</t>
+  </si>
+  <si>
+    <t>Product_Summary_Favourite_account_[WEB]</t>
+  </si>
+  <si>
+    <t>C70765</t>
+  </si>
+  <si>
     <t>on</t>
   </si>
   <si>
-    <t>off</t>
-  </si>
-  <si>
-    <t>Product_Summary_Favourite_account_[WEB]</t>
-  </si>
-  <si>
-    <t>C70765</t>
-  </si>
-  <si>
     <t>General-Dashboard-Quick_Links_[WEB]</t>
   </si>
   <si>
@@ -887,7 +887,7 @@
     <t>C70902</t>
   </si>
   <si>
-    <t>Payments_Own_Account_Transfer_To_Loan_[WEB]</t>
+    <t>Payments_Own_Account_Transfer_To_Loan_[WEB]-From_Current_Domestic_Account</t>
   </si>
   <si>
     <t>C70903</t>
@@ -996,6 +996,102 @@
   </si>
   <si>
     <t>Payments_Domestic_Payments_External_Non_Urgent_Payment_No_Model_[WEB]</t>
+  </si>
+  <si>
+    <t>Payments_Own_Account_Transfer_To_Loan_[WEB]-From_Savings_Account</t>
+  </si>
+  <si>
+    <t>C70915</t>
+  </si>
+  <si>
+    <t>Credit_Cards_Details_Card_Details_[WEB]</t>
+  </si>
+  <si>
+    <t>C70916</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments_[MOB_ANDROID]-Internal_Non_Urgent_Payment</t>
+  </si>
+  <si>
+    <t>C70917</t>
+  </si>
+  <si>
+    <t>Payments_Recipient_Last_5_Payments_Of_Recipient_[WEB]-View_And_Repeat</t>
+  </si>
+  <si>
+    <t>C70918</t>
+  </si>
+  <si>
+    <t>Payments_Payments_Arhive_Resubmit_Payments_From_Past_Payment_List_[WEB]-Internal_Transfer</t>
+  </si>
+  <si>
+    <t>C70919</t>
+  </si>
+  <si>
+    <t>Payments_Payments_Arhive_Resubmit_Payments_From_Past_Payment_List_[WEB]-Domestic_Payment</t>
+  </si>
+  <si>
+    <t>C70920</t>
+  </si>
+  <si>
+    <t>Payments_Payments_Arhive_Resubmit_Payments_From_Past_Payment_List_[WEB]-Prenesi</t>
+  </si>
+  <si>
+    <t>C70921</t>
+  </si>
+  <si>
+    <t>C70922</t>
+  </si>
+  <si>
+    <t>Payments_Specific_Payment_Credit_Card_Repayment_[WEB]-From_Current_Domestic_Account</t>
+  </si>
+  <si>
+    <t>C70923</t>
+  </si>
+  <si>
+    <t>Payments_Specific_Payment_Credit_Card_Repayment_[WEB]-From_Savings_Account</t>
+  </si>
+  <si>
+    <t>C70924</t>
+  </si>
+  <si>
+    <t>C70925</t>
+  </si>
+  <si>
+    <t>General_Dashboard_Page_overview_[WEB]</t>
+  </si>
+  <si>
+    <t>C70926</t>
+  </si>
+  <si>
+    <t>Credit_Cards_Details_Financial_Details_[WEB]</t>
+  </si>
+  <si>
+    <t>C70927</t>
+  </si>
+  <si>
+    <t>Credit_Cards_Transactions_List_[WEB]</t>
+  </si>
+  <si>
+    <t>C70928</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts_Transactions_Details_[WEB]</t>
+  </si>
+  <si>
+    <t>C70929</t>
+  </si>
+  <si>
+    <t>Current_Accounts_RSD_Statemants_Downloads_[WEB]</t>
+  </si>
+  <si>
+    <t>C70930</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts_Statemants_Downloads_[WEB]</t>
+  </si>
+  <si>
+    <t>C70931</t>
   </si>
 </sst>
 </file>
@@ -1615,7 +1711,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1623,6 +1719,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1676,18 +1775,6 @@
     <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1955,13 +2042,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F165"/>
+  <dimension ref="A1:F182"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="91.1388888888889" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" customFormat="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1998,16 +2085,16 @@
         <v>10</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" spans="1:6">
+      <c r="A3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
+      <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
@@ -2015,13 +2102,13 @@
         <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" spans="1:6">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -2038,10 +2125,10 @@
         <v>10</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" spans="1:6">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -2058,10 +2145,10 @@
         <v>10</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" spans="1:6">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -2075,13 +2162,13 @@
         <v>9</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" spans="1:6">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -2098,10 +2185,10 @@
         <v>10</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" spans="1:6">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -2118,10 +2205,10 @@
         <v>10</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" spans="1:6">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -2138,10 +2225,10 @@
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" customFormat="1" spans="1:6">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -2158,10 +2245,10 @@
         <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" customFormat="1" spans="1:6">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -2175,13 +2262,13 @@
         <v>9</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" customFormat="1" spans="1:6">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -2198,10 +2285,10 @@
         <v>10</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" customFormat="1" spans="1:6">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -2218,10 +2305,10 @@
         <v>10</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" customFormat="1" spans="1:6">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -2238,10 +2325,10 @@
         <v>10</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" customFormat="1" spans="1:6">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -2258,10 +2345,10 @@
         <v>10</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" customFormat="1" spans="1:6">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -2278,10 +2365,10 @@
         <v>10</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" customFormat="1" spans="1:6">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -2298,10 +2385,10 @@
         <v>10</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" customFormat="1" spans="1:6">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -2318,10 +2405,10 @@
         <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" customFormat="1" spans="1:6">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -2335,13 +2422,13 @@
         <v>9</v>
       </c>
       <c r="E19" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F19" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" customFormat="1" spans="1:6">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -2358,10 +2445,10 @@
         <v>10</v>
       </c>
       <c r="F20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" customFormat="1" spans="1:6">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -2378,10 +2465,10 @@
         <v>10</v>
       </c>
       <c r="F21" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" customFormat="1" spans="1:6">
       <c r="A22" t="s">
         <v>50</v>
       </c>
@@ -2398,10 +2485,10 @@
         <v>10</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" customFormat="1" spans="1:6">
       <c r="A23" t="s">
         <v>52</v>
       </c>
@@ -2418,10 +2505,10 @@
         <v>10</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" customFormat="1" spans="1:6">
       <c r="A24" t="s">
         <v>54</v>
       </c>
@@ -2435,13 +2522,13 @@
         <v>9</v>
       </c>
       <c r="E24" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" customFormat="1" spans="1:6">
       <c r="A25" t="s">
         <v>56</v>
       </c>
@@ -2458,10 +2545,10 @@
         <v>10</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" customFormat="1" spans="1:6">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -2478,10 +2565,10 @@
         <v>10</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" customFormat="1" spans="1:6">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -2498,10 +2585,10 @@
         <v>10</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" customFormat="1" spans="1:6">
       <c r="A28" t="s">
         <v>62</v>
       </c>
@@ -2515,13 +2602,13 @@
         <v>9</v>
       </c>
       <c r="E28" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" customFormat="1" spans="1:6">
       <c r="A29" t="s">
         <v>64</v>
       </c>
@@ -2538,10 +2625,10 @@
         <v>10</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" customFormat="1" spans="1:6">
       <c r="A30" t="s">
         <v>66</v>
       </c>
@@ -2558,10 +2645,10 @@
         <v>10</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" customFormat="1" spans="1:6">
       <c r="A31" t="s">
         <v>68</v>
       </c>
@@ -2578,10 +2665,10 @@
         <v>10</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" customFormat="1" spans="1:6">
       <c r="A32" t="s">
         <v>70</v>
       </c>
@@ -2598,10 +2685,10 @@
         <v>10</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" customFormat="1" spans="1:6">
       <c r="A33" t="s">
         <v>72</v>
       </c>
@@ -2618,10 +2705,10 @@
         <v>10</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" customFormat="1" spans="1:6">
       <c r="A34" t="s">
         <v>74</v>
       </c>
@@ -2638,10 +2725,10 @@
         <v>10</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" customFormat="1" spans="1:6">
       <c r="A35" t="s">
         <v>76</v>
       </c>
@@ -2655,13 +2742,13 @@
         <v>9</v>
       </c>
       <c r="E35" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" customFormat="1" spans="1:6">
       <c r="A36" t="s">
         <v>78</v>
       </c>
@@ -2675,13 +2762,13 @@
         <v>9</v>
       </c>
       <c r="E36" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" customFormat="1" spans="1:6">
       <c r="A37" t="s">
         <v>80</v>
       </c>
@@ -2698,10 +2785,10 @@
         <v>10</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" customFormat="1" spans="1:6">
       <c r="A38" t="s">
         <v>82</v>
       </c>
@@ -2718,10 +2805,10 @@
         <v>10</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" customFormat="1" spans="1:6">
       <c r="A39" t="s">
         <v>84</v>
       </c>
@@ -2735,13 +2822,13 @@
         <v>9</v>
       </c>
       <c r="E39" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" customFormat="1" spans="1:6">
       <c r="A40" t="s">
         <v>86</v>
       </c>
@@ -2755,13 +2842,13 @@
         <v>9</v>
       </c>
       <c r="E40" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" customFormat="1" spans="1:6">
       <c r="A41" t="s">
         <v>88</v>
       </c>
@@ -2778,10 +2865,10 @@
         <v>10</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" customFormat="1" spans="1:6">
       <c r="A42" t="s">
         <v>90</v>
       </c>
@@ -2795,13 +2882,13 @@
         <v>9</v>
       </c>
       <c r="E42" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F42" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" customFormat="1" spans="1:6">
       <c r="A43" t="s">
         <v>92</v>
       </c>
@@ -2818,10 +2905,10 @@
         <v>10</v>
       </c>
       <c r="F43" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" customFormat="1" spans="1:6">
       <c r="A44" t="s">
         <v>94</v>
       </c>
@@ -2838,10 +2925,10 @@
         <v>10</v>
       </c>
       <c r="F44" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" customFormat="1" spans="1:6">
       <c r="A45" t="s">
         <v>96</v>
       </c>
@@ -2858,10 +2945,10 @@
         <v>10</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" customFormat="1" spans="1:6">
       <c r="A46" t="s">
         <v>98</v>
       </c>
@@ -2878,10 +2965,10 @@
         <v>10</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" customFormat="1" spans="1:6">
       <c r="A47" t="s">
         <v>100</v>
       </c>
@@ -2898,10 +2985,10 @@
         <v>10</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48" customFormat="1" spans="1:6">
       <c r="A48" t="s">
         <v>102</v>
       </c>
@@ -2918,10 +3005,10 @@
         <v>10</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" customFormat="1" spans="1:6">
       <c r="A49" t="s">
         <v>104</v>
       </c>
@@ -2938,10 +3025,10 @@
         <v>10</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" customFormat="1" spans="1:6">
       <c r="A50" t="s">
         <v>106</v>
       </c>
@@ -2955,13 +3042,13 @@
         <v>9</v>
       </c>
       <c r="E50" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" customFormat="1" spans="1:6">
       <c r="A51" t="s">
         <v>108</v>
       </c>
@@ -2978,10 +3065,10 @@
         <v>10</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" customFormat="1" spans="1:6">
       <c r="A52" t="s">
         <v>110</v>
       </c>
@@ -2998,10 +3085,10 @@
         <v>10</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" customFormat="1" spans="1:6">
       <c r="A53" t="s">
         <v>112</v>
       </c>
@@ -3015,13 +3102,13 @@
         <v>9</v>
       </c>
       <c r="E53" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" customFormat="1" spans="1:6">
       <c r="A54" t="s">
         <v>114</v>
       </c>
@@ -3035,13 +3122,13 @@
         <v>9</v>
       </c>
       <c r="E54" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" customFormat="1" spans="1:6">
       <c r="A55" t="s">
         <v>116</v>
       </c>
@@ -3055,13 +3142,13 @@
         <v>9</v>
       </c>
       <c r="E55" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56" customFormat="1" spans="1:6">
       <c r="A56" t="s">
         <v>118</v>
       </c>
@@ -3078,10 +3165,10 @@
         <v>10</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" customFormat="1" spans="1:6">
       <c r="A57" t="s">
         <v>120</v>
       </c>
@@ -3098,10 +3185,10 @@
         <v>10</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" customFormat="1" spans="1:6">
       <c r="A58" t="s">
         <v>122</v>
       </c>
@@ -3115,13 +3202,13 @@
         <v>9</v>
       </c>
       <c r="E58" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" customFormat="1" spans="1:6">
       <c r="A59" t="s">
         <v>124</v>
       </c>
@@ -3138,10 +3225,10 @@
         <v>10</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" customFormat="1" spans="1:6">
       <c r="A60" t="s">
         <v>126</v>
       </c>
@@ -3158,10 +3245,10 @@
         <v>10</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" customFormat="1" spans="1:6">
       <c r="A61" t="s">
         <v>128</v>
       </c>
@@ -3178,10 +3265,10 @@
         <v>10</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62" customFormat="1" spans="1:6">
       <c r="A62" t="s">
         <v>130</v>
       </c>
@@ -3198,10 +3285,10 @@
         <v>10</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" customFormat="1" spans="1:6">
       <c r="A63" t="s">
         <v>132</v>
       </c>
@@ -3215,13 +3302,13 @@
         <v>9</v>
       </c>
       <c r="E63" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64" customFormat="1" spans="1:6">
       <c r="A64" t="s">
         <v>134</v>
       </c>
@@ -3238,10 +3325,10 @@
         <v>10</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65" customFormat="1" spans="1:6">
       <c r="A65" t="s">
         <v>136</v>
       </c>
@@ -3258,10 +3345,10 @@
         <v>10</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="66" customFormat="1" spans="1:6">
       <c r="A66" t="s">
         <v>138</v>
       </c>
@@ -3278,10 +3365,10 @@
         <v>10</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" customFormat="1" spans="1:6">
       <c r="A67" t="s">
         <v>140</v>
       </c>
@@ -3298,10 +3385,10 @@
         <v>10</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="68" customFormat="1" spans="1:6">
       <c r="A68" t="s">
         <v>142</v>
       </c>
@@ -3318,10 +3405,10 @@
         <v>10</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69" customFormat="1" spans="1:6">
       <c r="A69" t="s">
         <v>144</v>
       </c>
@@ -3338,10 +3425,10 @@
         <v>10</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="70" customFormat="1" spans="1:6">
       <c r="A70" t="s">
         <v>146</v>
       </c>
@@ -3358,10 +3445,10 @@
         <v>10</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="71" customFormat="1" spans="1:6">
       <c r="A71" t="s">
         <v>148</v>
       </c>
@@ -3378,10 +3465,10 @@
         <v>10</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72" customFormat="1" spans="1:6">
       <c r="A72" t="s">
         <v>150</v>
       </c>
@@ -3398,10 +3485,10 @@
         <v>10</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" customFormat="1" spans="1:6">
       <c r="A73" t="s">
         <v>152</v>
       </c>
@@ -3418,10 +3505,10 @@
         <v>10</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="74" customFormat="1" spans="1:6">
       <c r="A74" t="s">
         <v>154</v>
       </c>
@@ -3438,10 +3525,10 @@
         <v>10</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="75" customFormat="1" spans="1:6">
       <c r="A75" t="s">
         <v>156</v>
       </c>
@@ -3458,10 +3545,10 @@
         <v>10</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="76" customFormat="1" spans="1:6">
       <c r="A76" t="s">
         <v>158</v>
       </c>
@@ -3478,10 +3565,10 @@
         <v>10</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77" customFormat="1" spans="1:6">
       <c r="A77" t="s">
         <v>160</v>
       </c>
@@ -3498,10 +3585,10 @@
         <v>10</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="78" customFormat="1" spans="1:6">
       <c r="A78" t="s">
         <v>162</v>
       </c>
@@ -3518,10 +3605,10 @@
         <v>10</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="79" customFormat="1" spans="1:6">
       <c r="A79" t="s">
         <v>164</v>
       </c>
@@ -3538,10 +3625,10 @@
         <v>10</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="80" customFormat="1" spans="1:6">
       <c r="A80" t="s">
         <v>166</v>
       </c>
@@ -3558,10 +3645,10 @@
         <v>10</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="81" customFormat="1" spans="1:6">
       <c r="A81" t="s">
         <v>168</v>
       </c>
@@ -3575,13 +3662,13 @@
         <v>9</v>
       </c>
       <c r="E81" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="82" customFormat="1" spans="1:6">
       <c r="A82" t="s">
         <v>170</v>
       </c>
@@ -3598,10 +3685,10 @@
         <v>10</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="83" customFormat="1" spans="1:6">
       <c r="A83" t="s">
         <v>172</v>
       </c>
@@ -3618,10 +3705,10 @@
         <v>10</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" customFormat="1" spans="1:6">
       <c r="A84" t="s">
         <v>174</v>
       </c>
@@ -3638,10 +3725,10 @@
         <v>10</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="85" customFormat="1" spans="1:6">
       <c r="A85" t="s">
         <v>176</v>
       </c>
@@ -3658,10 +3745,10 @@
         <v>10</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="86" customFormat="1" spans="1:6">
       <c r="A86" t="s">
         <v>178</v>
       </c>
@@ -3678,10 +3765,10 @@
         <v>10</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="87" customFormat="1" spans="1:6">
       <c r="A87" t="s">
         <v>166</v>
       </c>
@@ -3698,10 +3785,10 @@
         <v>10</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="88" customFormat="1" spans="1:6">
       <c r="A88" t="s">
         <v>181</v>
       </c>
@@ -3715,13 +3802,13 @@
         <v>9</v>
       </c>
       <c r="E88" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="89" customFormat="1" spans="1:6">
       <c r="A89" t="s">
         <v>183</v>
       </c>
@@ -3738,10 +3825,10 @@
         <v>10</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90" customFormat="1" spans="1:6">
       <c r="A90" t="s">
         <v>185</v>
       </c>
@@ -3758,10 +3845,10 @@
         <v>10</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="91" customFormat="1" spans="1:6">
       <c r="A91" t="s">
         <v>187</v>
       </c>
@@ -3778,10 +3865,10 @@
         <v>10</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92" customFormat="1" spans="1:6">
       <c r="A92" t="s">
         <v>189</v>
       </c>
@@ -3798,10 +3885,10 @@
         <v>10</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="93" customFormat="1" spans="1:6">
       <c r="A93" t="s">
         <v>191</v>
       </c>
@@ -3818,10 +3905,10 @@
         <v>10</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="94" customFormat="1" spans="1:6">
       <c r="A94" t="s">
         <v>193</v>
       </c>
@@ -3838,10 +3925,10 @@
         <v>10</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95" customFormat="1" spans="1:6">
       <c r="A95" t="s">
         <v>195</v>
       </c>
@@ -3858,10 +3945,10 @@
         <v>10</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="96" customFormat="1" spans="1:6">
       <c r="A96" t="s">
         <v>197</v>
       </c>
@@ -3878,10 +3965,10 @@
         <v>10</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="97" customFormat="1" spans="1:6">
       <c r="A97" t="s">
         <v>199</v>
       </c>
@@ -3898,10 +3985,10 @@
         <v>10</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="98" customFormat="1" spans="1:6">
       <c r="A98" t="s">
         <v>201</v>
       </c>
@@ -3918,10 +4005,10 @@
         <v>10</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="99" customFormat="1" spans="1:6">
       <c r="A99" t="s">
         <v>203</v>
       </c>
@@ -3938,10 +4025,10 @@
         <v>10</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="100" customFormat="1" spans="1:6">
       <c r="A100" t="s">
         <v>205</v>
       </c>
@@ -3958,10 +4045,10 @@
         <v>10</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" customFormat="1" spans="1:6">
       <c r="A101" t="s">
         <v>207</v>
       </c>
@@ -3978,10 +4065,10 @@
         <v>10</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="102" customFormat="1" spans="1:6">
       <c r="A102" t="s">
         <v>209</v>
       </c>
@@ -3998,10 +4085,10 @@
         <v>10</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="103" customFormat="1" spans="1:6">
       <c r="A103" t="s">
         <v>211</v>
       </c>
@@ -4018,10 +4105,10 @@
         <v>10</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="104" customFormat="1" spans="1:6">
       <c r="A104" t="s">
         <v>213</v>
       </c>
@@ -4035,13 +4122,13 @@
         <v>9</v>
       </c>
       <c r="E104" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="105" customFormat="1" spans="1:6">
       <c r="A105" t="s">
         <v>215</v>
       </c>
@@ -4055,13 +4142,13 @@
         <v>9</v>
       </c>
       <c r="E105" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="106" customFormat="1" spans="1:6">
       <c r="A106" t="s">
         <v>217</v>
       </c>
@@ -4075,13 +4162,13 @@
         <v>9</v>
       </c>
       <c r="E106" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="107" customFormat="1" spans="1:6">
       <c r="A107" t="s">
         <v>219</v>
       </c>
@@ -4095,13 +4182,13 @@
         <v>9</v>
       </c>
       <c r="E107" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="108" customFormat="1" spans="1:6">
       <c r="A108" t="s">
         <v>221</v>
       </c>
@@ -4118,10 +4205,10 @@
         <v>10</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="109" customFormat="1" spans="1:6">
       <c r="A109" t="s">
         <v>223</v>
       </c>
@@ -4138,10 +4225,10 @@
         <v>10</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="110" customFormat="1" spans="1:6">
       <c r="A110" t="s">
         <v>225</v>
       </c>
@@ -4158,10 +4245,10 @@
         <v>10</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="111" customFormat="1" spans="1:6">
       <c r="A111" t="s">
         <v>227</v>
       </c>
@@ -4175,13 +4262,13 @@
         <v>9</v>
       </c>
       <c r="E111" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="112" customFormat="1" spans="1:6">
       <c r="A112" t="s">
         <v>229</v>
       </c>
@@ -4198,10 +4285,10 @@
         <v>10</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="113" customFormat="1" spans="1:6">
       <c r="A113" t="s">
         <v>231</v>
       </c>
@@ -4218,10 +4305,10 @@
         <v>10</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="114" customFormat="1" spans="1:6">
       <c r="A114" t="s">
         <v>233</v>
       </c>
@@ -4238,10 +4325,10 @@
         <v>10</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="115" customFormat="1" spans="1:6">
       <c r="A115" t="s">
         <v>235</v>
       </c>
@@ -4255,13 +4342,13 @@
         <v>9</v>
       </c>
       <c r="E115" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="116" customFormat="1" spans="1:6">
       <c r="A116" t="s">
         <v>237</v>
       </c>
@@ -4275,13 +4362,13 @@
         <v>9</v>
       </c>
       <c r="E116" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="117" customFormat="1" spans="1:6">
       <c r="A117" t="s">
         <v>239</v>
       </c>
@@ -4295,13 +4382,13 @@
         <v>9</v>
       </c>
       <c r="E117" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="118" customFormat="1" spans="1:6">
       <c r="A118" t="s">
         <v>241</v>
       </c>
@@ -4318,10 +4405,10 @@
         <v>10</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="119" customFormat="1" spans="1:6">
       <c r="A119" t="s">
         <v>243</v>
       </c>
@@ -4335,13 +4422,13 @@
         <v>9</v>
       </c>
       <c r="E119" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="120" customFormat="1" spans="1:6">
       <c r="A120" t="s">
         <v>245</v>
       </c>
@@ -4358,10 +4445,10 @@
         <v>10</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="121" customFormat="1" spans="1:6">
       <c r="A121" t="s">
         <v>247</v>
       </c>
@@ -4378,10 +4465,10 @@
         <v>10</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="122" customFormat="1" spans="1:6">
       <c r="A122" t="s">
         <v>249</v>
       </c>
@@ -4398,10 +4485,10 @@
         <v>10</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="123" customFormat="1" spans="1:6">
       <c r="A123" t="s">
         <v>251</v>
       </c>
@@ -4415,13 +4502,13 @@
         <v>9</v>
       </c>
       <c r="E123" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="124" customFormat="1" spans="1:6">
       <c r="A124" t="s">
         <v>253</v>
       </c>
@@ -4435,13 +4522,13 @@
         <v>9</v>
       </c>
       <c r="E124" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="125" customFormat="1" spans="1:6">
       <c r="A125" t="s">
         <v>255</v>
       </c>
@@ -4455,13 +4542,13 @@
         <v>9</v>
       </c>
       <c r="E125" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="126" customFormat="1" spans="1:6">
       <c r="A126" t="s">
         <v>257</v>
       </c>
@@ -4478,10 +4565,10 @@
         <v>10</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="127" customFormat="1" spans="1:6">
       <c r="A127" t="s">
         <v>259</v>
       </c>
@@ -4498,10 +4585,10 @@
         <v>10</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="128" customFormat="1" spans="1:6">
       <c r="A128" t="s">
         <v>261</v>
       </c>
@@ -4518,10 +4605,10 @@
         <v>10</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="129" customFormat="1" spans="1:6">
       <c r="A129" t="s">
         <v>263</v>
       </c>
@@ -4535,13 +4622,13 @@
         <v>9</v>
       </c>
       <c r="E129" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="130" customFormat="1" spans="1:6">
       <c r="A130" t="s">
         <v>265</v>
       </c>
@@ -4555,13 +4642,13 @@
         <v>9</v>
       </c>
       <c r="E130" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="131" customFormat="1" spans="1:6">
       <c r="A131" t="s">
         <v>267</v>
       </c>
@@ -4575,13 +4662,13 @@
         <v>9</v>
       </c>
       <c r="E131" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="132" customFormat="1" spans="1:6">
       <c r="A132" t="s">
         <v>269</v>
       </c>
@@ -4595,13 +4682,13 @@
         <v>9</v>
       </c>
       <c r="E132" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="133" customFormat="1" spans="1:6">
       <c r="A133" t="s">
         <v>271</v>
       </c>
@@ -4615,10 +4702,10 @@
         <v>9</v>
       </c>
       <c r="E133" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="134" customFormat="1" spans="1:6">
@@ -4635,10 +4722,10 @@
         <v>9</v>
       </c>
       <c r="E134" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="135" customFormat="1" spans="1:6">
@@ -4655,10 +4742,10 @@
         <v>9</v>
       </c>
       <c r="E135" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="136" customFormat="1" spans="1:6">
@@ -4675,10 +4762,10 @@
         <v>9</v>
       </c>
       <c r="E136" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="137" customFormat="1" spans="1:6">
@@ -4695,13 +4782,13 @@
         <v>9</v>
       </c>
       <c r="E137" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="138" customFormat="1" spans="1:6">
       <c r="A138" t="s">
         <v>282</v>
       </c>
@@ -4715,13 +4802,13 @@
         <v>9</v>
       </c>
       <c r="E138" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="139" customFormat="1" spans="1:6">
       <c r="A139" t="s">
         <v>284</v>
       </c>
@@ -4735,13 +4822,13 @@
         <v>9</v>
       </c>
       <c r="E139" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="140" customFormat="1" spans="1:6">
       <c r="A140" t="s">
         <v>286</v>
       </c>
@@ -4755,13 +4842,13 @@
         <v>9</v>
       </c>
       <c r="E140" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="141" customFormat="1" spans="1:6">
       <c r="A141" t="s">
         <v>288</v>
       </c>
@@ -4775,13 +4862,13 @@
         <v>9</v>
       </c>
       <c r="E141" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="142" customFormat="1" spans="1:6">
       <c r="A142" t="s">
         <v>290</v>
       </c>
@@ -4795,13 +4882,13 @@
         <v>9</v>
       </c>
       <c r="E142" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="143" customFormat="1" spans="1:6">
       <c r="A143" t="s">
         <v>292</v>
       </c>
@@ -4815,13 +4902,13 @@
         <v>9</v>
       </c>
       <c r="E143" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="144" customFormat="1" spans="1:6">
       <c r="A144" t="s">
         <v>294</v>
       </c>
@@ -4835,13 +4922,13 @@
         <v>9</v>
       </c>
       <c r="E144" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="145" customFormat="1" spans="1:6">
       <c r="A145" t="s">
         <v>296</v>
       </c>
@@ -4855,13 +4942,13 @@
         <v>9</v>
       </c>
       <c r="E145" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="146" customFormat="1" spans="1:6">
       <c r="A146" t="s">
         <v>298</v>
       </c>
@@ -4875,13 +4962,13 @@
         <v>9</v>
       </c>
       <c r="E146" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="147" customFormat="1" spans="1:6">
       <c r="A147" t="s">
         <v>280</v>
       </c>
@@ -4895,13 +4982,13 @@
         <v>9</v>
       </c>
       <c r="E147" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="148" customFormat="1" spans="1:6">
       <c r="A148" t="s">
         <v>301</v>
       </c>
@@ -4915,13 +5002,13 @@
         <v>9</v>
       </c>
       <c r="E148" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="149" customFormat="1" spans="1:6">
       <c r="A149" t="s">
         <v>303</v>
       </c>
@@ -4935,13 +5022,13 @@
         <v>9</v>
       </c>
       <c r="E149" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="150" customFormat="1" spans="1:6">
       <c r="A150" t="s">
         <v>305</v>
       </c>
@@ -4955,13 +5042,13 @@
         <v>9</v>
       </c>
       <c r="E150" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="151" customFormat="1" spans="1:6">
       <c r="A151" t="s">
         <v>307</v>
       </c>
@@ -4975,13 +5062,13 @@
         <v>9</v>
       </c>
       <c r="E151" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="152" customFormat="1" spans="1:6">
       <c r="A152" t="s">
         <v>309</v>
       </c>
@@ -4995,13 +5082,13 @@
         <v>9</v>
       </c>
       <c r="E152" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="153" customFormat="1" spans="1:6">
       <c r="A153" t="s">
         <v>310</v>
       </c>
@@ -5018,10 +5105,10 @@
         <v>10</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="154" customFormat="1" spans="1:6">
       <c r="A154" t="s">
         <v>311</v>
       </c>
@@ -5035,13 +5122,13 @@
         <v>9</v>
       </c>
       <c r="E154" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="155" customFormat="1" spans="1:6">
       <c r="A155" t="s">
         <v>312</v>
       </c>
@@ -5055,13 +5142,13 @@
         <v>9</v>
       </c>
       <c r="E155" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="156" customFormat="1" spans="1:6">
       <c r="A156" t="s">
         <v>313</v>
       </c>
@@ -5075,13 +5162,13 @@
         <v>9</v>
       </c>
       <c r="E156" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="157" customFormat="1" spans="1:6">
       <c r="A157" t="s">
         <v>314</v>
       </c>
@@ -5095,13 +5182,13 @@
         <v>9</v>
       </c>
       <c r="E157" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="158" customFormat="1" spans="1:6">
       <c r="A158" t="s">
         <v>315</v>
       </c>
@@ -5115,13 +5202,13 @@
         <v>9</v>
       </c>
       <c r="E158" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="159" customFormat="1" spans="1:6">
       <c r="A159" t="s">
         <v>316</v>
       </c>
@@ -5135,13 +5222,13 @@
         <v>9</v>
       </c>
       <c r="E159" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="160" customFormat="1" spans="1:6">
       <c r="A160" t="s">
         <v>317</v>
       </c>
@@ -5155,13 +5242,13 @@
         <v>9</v>
       </c>
       <c r="E160" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="161" customFormat="1" spans="1:6">
       <c r="A161" t="s">
         <v>318</v>
       </c>
@@ -5175,13 +5262,13 @@
         <v>9</v>
       </c>
       <c r="E161" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="162" customFormat="1" spans="1:6">
       <c r="A162" t="s">
         <v>319</v>
       </c>
@@ -5195,13 +5282,13 @@
         <v>9</v>
       </c>
       <c r="E162" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="163" customFormat="1" spans="1:6">
       <c r="A163" t="s">
         <v>320</v>
       </c>
@@ -5215,13 +5302,13 @@
         <v>9</v>
       </c>
       <c r="E163" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="164" customFormat="1" spans="1:6">
       <c r="A164" t="s">
         <v>321</v>
       </c>
@@ -5235,13 +5322,13 @@
         <v>9</v>
       </c>
       <c r="E164" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="165" customFormat="1" spans="1:6">
       <c r="A165" t="s">
         <v>322</v>
       </c>
@@ -5255,46 +5342,353 @@
         <v>9</v>
       </c>
       <c r="E165" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="166" customFormat="1" spans="1:6">
+      <c r="A166" t="s">
+        <v>323</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E166" t="s">
+        <v>13</v>
+      </c>
+      <c r="F166" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="167" customFormat="1" spans="1:6">
+      <c r="A167" t="s">
+        <v>325</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="C167" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E167" t="s">
+        <v>13</v>
+      </c>
+      <c r="F167" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="168" customFormat="1" spans="1:6">
+      <c r="A168" t="s">
+        <v>327</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="C168" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D168" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E168" t="s">
+        <v>13</v>
+      </c>
+      <c r="F168" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="169" customFormat="1" spans="1:6">
+      <c r="A169" t="s">
+        <v>329</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="C169" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E169" t="s">
+        <v>13</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="170" customFormat="1" ht="15" customHeight="1" spans="1:6">
+      <c r="A170" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="C170" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E170" t="s">
+        <v>13</v>
+      </c>
+      <c r="F170" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="171" customFormat="1" spans="1:6">
+      <c r="A171" t="s">
+        <v>333</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="C171" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E171" t="s">
+        <v>13</v>
+      </c>
+      <c r="F171" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="172" customFormat="1" spans="1:6">
+      <c r="A172" t="s">
+        <v>335</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="C172" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E172" t="s">
+        <v>13</v>
+      </c>
+      <c r="F172" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="173" customFormat="1" spans="1:6">
+      <c r="A173" t="s">
+        <v>168</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="C173" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E173" t="s">
+        <v>13</v>
+      </c>
+      <c r="F173" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="174" customFormat="1" spans="1:6">
+      <c r="A174" t="s">
+        <v>338</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="C174" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D174" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E174" t="s">
+        <v>13</v>
+      </c>
+      <c r="F174" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="175" customFormat="1" spans="1:6">
+      <c r="A175" t="s">
+        <v>340</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C175" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D175" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E175" t="s">
+        <v>13</v>
+      </c>
+      <c r="F175" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="176" customFormat="1" spans="1:6">
+      <c r="A176" t="s">
+        <v>310</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C176" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D176" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E176" t="s">
+        <v>13</v>
+      </c>
+      <c r="F176" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="177" customFormat="1" spans="1:6">
+      <c r="A177" t="s">
+        <v>343</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C177" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D177" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E177" t="s">
+        <v>13</v>
+      </c>
+      <c r="F177" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="178" customFormat="1" spans="1:6">
+      <c r="A178" t="s">
+        <v>345</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="C178" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E178" t="s">
+        <v>13</v>
+      </c>
+      <c r="F178" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="179" customFormat="1" spans="1:6">
+      <c r="A179" t="s">
+        <v>347</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="C179" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D179" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E179" t="s">
+        <v>13</v>
+      </c>
+      <c r="F179" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="180" customFormat="1" spans="1:6">
+      <c r="A180" t="s">
+        <v>349</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C180" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E180" t="s">
+        <v>13</v>
+      </c>
+      <c r="F180" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6">
+      <c r="A181" t="s">
+        <v>351</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C181" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E181" t="s">
+        <v>13</v>
+      </c>
+      <c r="F181" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6">
+      <c r="A182" t="s">
+        <v>353</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="C182" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E182" t="s">
+        <v>13</v>
+      </c>
+      <c r="F182" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B138">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B148">
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A149">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B149">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A150">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B150">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A151">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B151">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B152:B165">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B137 B139:B147 B166:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>

--- a/testdata/listForExecution.xlsx
+++ b/testdata/listForExecution.xlsx
@@ -4,11 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="27945" windowHeight="12180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$165</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -27,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1092" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="342">
   <si>
     <t>TestName</t>
   </si>
@@ -59,6 +62,9 @@
     <t>data</t>
   </si>
   <si>
+    <t>on</t>
+  </si>
+  <si>
     <t>off</t>
   </si>
   <si>
@@ -68,9 +74,6 @@
     <t>C70765</t>
   </si>
   <si>
-    <t>on</t>
-  </si>
-  <si>
     <t>General-Dashboard-Quick_Links_[WEB]</t>
   </si>
   <si>
@@ -155,7 +158,7 @@
     <t>C70779</t>
   </si>
   <si>
-    <t>General-Dashboard-Page_overview_[WEB]</t>
+    <t>General_Dashboard_Page_overview_[WEB]</t>
   </si>
   <si>
     <t>C70780</t>
@@ -875,223 +878,184 @@
     <t>C70900</t>
   </si>
   <si>
-    <t>Payments_Currency_Exchange_Pricelist_[WEB]-Overview</t>
+    <t>Payments_Domestic_Payments_Internal_Urgent_Payment_[WEB]</t>
   </si>
   <si>
     <t>C70901</t>
   </si>
   <si>
+    <t>Payments_Domestic_Payments_Internal_Non_Urgent_Payment_[WEB]</t>
+  </si>
+  <si>
+    <t>C70902</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_External_Urgent_Payment_No_Model_[WEB]</t>
+  </si>
+  <si>
+    <t>C70903</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_External_Urgent_Payment_Model11_Invalid_Bez_Poziva_Na_Broj_[WEB]</t>
+  </si>
+  <si>
+    <t>C70904</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_External_Non_Urgent_Payment_Model11_[WEB]</t>
+  </si>
+  <si>
+    <t>C70905</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_External_Urgent_Payment_Model97_Invalid_Bez_Poziva_Na_Broj_[WEB]</t>
+  </si>
+  <si>
+    <t>C70906</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_External_Non_Urgent_Payment_Model97_[WEB]</t>
+  </si>
+  <si>
+    <t>C70907</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_Budzetski_Urgent_Payment_Purpose_Code_289_Invalid_[WEB]</t>
+  </si>
+  <si>
+    <t>C70908</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_Budzetski_Urgent_Payment_Without_Reference_Number_Invalid_[WEB]</t>
+  </si>
+  <si>
+    <t>C70909</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_Budzetski_Urgent_Payment_Model97_[WEB]</t>
+  </si>
+  <si>
+    <t>C70910</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_Budzetski_Non_Urgent_Payment_Model97_[WEB]</t>
+  </si>
+  <si>
+    <t>C70911</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_External_Urgent_Payment_Model97_[WEB]</t>
+  </si>
+  <si>
+    <t>C70912</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_External_Urgent_Payment_Model11_[WEB]</t>
+  </si>
+  <si>
+    <t>C70913</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_External_Non_Urgent_Payment_No_Model_[WEB]</t>
+  </si>
+  <si>
+    <t>C70914</t>
+  </si>
+  <si>
+    <t>Payments_Recipient_Last_5_Payments_Of_Recipient_[WEB]-View_And_Repeat</t>
+  </si>
+  <si>
+    <t>C70915</t>
+  </si>
+  <si>
+    <t>Payments_Own_Account_Transfer_From_Current_Foreign_Account_To_Current_Foreign_Account_[WEB]</t>
+  </si>
+  <si>
+    <t>C70916</t>
+  </si>
+  <si>
+    <t>Payments_Own_Account_Transfer_To_Loan_[WEB]</t>
+  </si>
+  <si>
+    <t>C70917</t>
+  </si>
+  <si>
+    <t>Payments_Payments_Archive_Payments_Details_[WEB]</t>
+  </si>
+  <si>
+    <t>C70918</t>
+  </si>
+  <si>
+    <t>Payments_Upcoming_Payments_Details_Of_Payments_Transaction_On_The_List_Of_Transaction_[WEB]</t>
+  </si>
+  <si>
+    <t>C70919</t>
+  </si>
+  <si>
+    <t>Payments_Currency_Exchange_[WEB]-Buy_From_Payment</t>
+  </si>
+  <si>
+    <t>C70920</t>
+  </si>
+  <si>
+    <t>Payments_Currency_Exchange_[WEB]-Sell_From_Payment</t>
+  </si>
+  <si>
+    <t>C70921</t>
+  </si>
+  <si>
     <t>Saving_Accounts_Transactions_Download_Option_[WEB]</t>
   </si>
   <si>
-    <t>C70902</t>
-  </si>
-  <si>
-    <t>Payments_Own_Account_Transfer_To_Loan_[WEB]-From_Current_Domestic_Account</t>
-  </si>
-  <si>
-    <t>C70903</t>
-  </si>
-  <si>
-    <t>Payments_Own_Account_Transfer_From_Current_Foreign_Account_To_Current_Foreign_Account_[WEB]</t>
-  </si>
-  <si>
-    <t>C70904</t>
-  </si>
-  <si>
-    <t>Payments_Currency_Exchange_[WEB]-Buy_From_Payment</t>
-  </si>
-  <si>
-    <t>C70905</t>
-  </si>
-  <si>
-    <t>Payments_Currency_Exchange_[WEB]-Sell_From_Payment</t>
-  </si>
-  <si>
-    <t>C70906</t>
+    <t>C70922</t>
   </si>
   <si>
     <t>Savings_Accounts_Transactions_Filter_By_Date_Date_Picker_[WEB]</t>
   </si>
   <si>
-    <t>C70907</t>
+    <t>C70923</t>
   </si>
   <si>
     <t>Payments_Recipient_Template_List_[WEB]</t>
   </si>
   <si>
-    <t>C70908</t>
-  </si>
-  <si>
-    <t>Payments_Upcoming_Payments_Details_Of_Payments_Transaction_On_The_List_Of_Transaction_[WEB]</t>
-  </si>
-  <si>
-    <t>C70909</t>
-  </si>
-  <si>
-    <t>C70910</t>
-  </si>
-  <si>
-    <t>Payments_Payments_Archive_Payments_Details_[WEB]</t>
-  </si>
-  <si>
-    <t>C70911</t>
-  </si>
-  <si>
-    <t>Current_Accounts_RSD_Statemants_List_[WEB]</t>
-  </si>
-  <si>
-    <t>C70912</t>
-  </si>
-  <si>
-    <t>Current_Foreign_Accounts_Statemants_List_[WEB]</t>
-  </si>
-  <si>
-    <t>C70913</t>
-  </si>
-  <si>
-    <t>Saving_Accounts_Accounts_Statemants_List_[WEB]</t>
-  </si>
-  <si>
-    <t>C70914</t>
-  </si>
-  <si>
-    <t>Payments_Domestic_Payments_Internal_Urgent_Payment_[WEB]</t>
-  </si>
-  <si>
-    <t>Payments_Domestic_Payments_Internal_Non_Urgent_Payment_[WEB]</t>
-  </si>
-  <si>
-    <t>Payments_Domestic_Payments_External_Urgent_Payment_No_Model_[WEB]</t>
-  </si>
-  <si>
-    <t>Payments_Domestic_Payments_External_Urgent_Payment_Model11_Invalid_Bez_Poziva_Na_Broj_[WEB]</t>
-  </si>
-  <si>
-    <t>Payments_Domestic_Payments_External_Non_Urgent_Payment_Model11_[WEB]</t>
-  </si>
-  <si>
-    <t>Payments_Domestic_Payments_External_Urgent_Payment_Model97_Invalid_Bez_Poziva_Na_Broj_[WEB]</t>
-  </si>
-  <si>
-    <t>Payments_Domestic_Payments_External_Non_Urgent_Payment_Model97_[WEB]</t>
-  </si>
-  <si>
-    <t>Payments_Domestic_Payments_Budzetski_Urgent_Payment_Purpose_Code_289_Invalid_[WEB]</t>
-  </si>
-  <si>
-    <t>Payments_Domestic_Payments_Budzetski_Urgent_Payment_Without_Reference_Number_Invalid_[WEB]</t>
-  </si>
-  <si>
-    <t>Payments_Domestic_Payments_Budzetski_Urgent_Payment_Model97_[WEB]</t>
-  </si>
-  <si>
-    <t>Payments_Domestic_Payments_Budzetski_Non_Urgent_Payment_Model97_[WEB]</t>
-  </si>
-  <si>
-    <t>Payments_Domestic_Payments_External_Urgent_Payment_Model97_[WEB]</t>
-  </si>
-  <si>
-    <t>Payments_Domestic_Payments_External_Urgent_Payment_Model11_[WEB]</t>
-  </si>
-  <si>
-    <t>Payments_Domestic_Payments_External_Non_Urgent_Payment_No_Model_[WEB]</t>
-  </si>
-  <si>
-    <t>Payments_Own_Account_Transfer_To_Loan_[WEB]-From_Savings_Account</t>
-  </si>
-  <si>
-    <t>C70915</t>
+    <t>C70924</t>
   </si>
   <si>
     <t>Credit_Cards_Details_Card_Details_[WEB]</t>
   </si>
   <si>
-    <t>C70916</t>
-  </si>
-  <si>
-    <t>Payments-Domestic_Payments_[MOB_ANDROID]-Internal_Non_Urgent_Payment</t>
-  </si>
-  <si>
-    <t>C70917</t>
-  </si>
-  <si>
-    <t>Payments_Recipient_Last_5_Payments_Of_Recipient_[WEB]-View_And_Repeat</t>
-  </si>
-  <si>
-    <t>C70918</t>
+    <t>C70925</t>
   </si>
   <si>
     <t>Payments_Payments_Arhive_Resubmit_Payments_From_Past_Payment_List_[WEB]-Internal_Transfer</t>
   </si>
   <si>
-    <t>C70919</t>
+    <t>C70926</t>
+  </si>
+  <si>
+    <t>Payments_Specific_Payment_Credit_Card_Repayment_[WEB]-From_Current_Domestic_Account</t>
+  </si>
+  <si>
+    <t>C70927</t>
+  </si>
+  <si>
+    <t>Payments_Specific_Payment_Credit_Card_Repayment_[WEB]-From_Savings_Account</t>
+  </si>
+  <si>
+    <t>C70928</t>
   </si>
   <si>
     <t>Payments_Payments_Arhive_Resubmit_Payments_From_Past_Payment_List_[WEB]-Domestic_Payment</t>
   </si>
   <si>
-    <t>C70920</t>
+    <t>C70929</t>
   </si>
   <si>
     <t>Payments_Payments_Arhive_Resubmit_Payments_From_Past_Payment_List_[WEB]-Prenesi</t>
   </si>
   <si>
-    <t>C70921</t>
-  </si>
-  <si>
-    <t>C70922</t>
-  </si>
-  <si>
-    <t>Payments_Specific_Payment_Credit_Card_Repayment_[WEB]-From_Current_Domestic_Account</t>
-  </si>
-  <si>
-    <t>C70923</t>
-  </si>
-  <si>
-    <t>Payments_Specific_Payment_Credit_Card_Repayment_[WEB]-From_Savings_Account</t>
-  </si>
-  <si>
-    <t>C70924</t>
-  </si>
-  <si>
-    <t>C70925</t>
-  </si>
-  <si>
-    <t>General_Dashboard_Page_overview_[WEB]</t>
-  </si>
-  <si>
-    <t>C70926</t>
-  </si>
-  <si>
-    <t>Credit_Cards_Details_Financial_Details_[WEB]</t>
-  </si>
-  <si>
-    <t>C70927</t>
-  </si>
-  <si>
-    <t>Credit_Cards_Transactions_List_[WEB]</t>
-  </si>
-  <si>
-    <t>C70928</t>
-  </si>
-  <si>
-    <t>Current_Foreign_Accounts_Transactions_Details_[WEB]</t>
-  </si>
-  <si>
-    <t>C70929</t>
-  </si>
-  <si>
-    <t>Current_Accounts_RSD_Statemants_Downloads_[WEB]</t>
-  </si>
-  <si>
     <t>C70930</t>
-  </si>
-  <si>
-    <t>Current_Foreign_Accounts_Statemants_Downloads_[WEB]</t>
-  </si>
-  <si>
-    <t>C70931</t>
   </si>
 </sst>
 </file>
@@ -1716,12 +1680,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1775,6 +1739,18 @@
     <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2042,20 +2018,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F182"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <dimension ref="A1:F167"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="91.1388888888889" customWidth="1"/>
+    <col min="1" max="1" width="94.1428571428571" customWidth="1"/>
+    <col min="2" max="2" width="11.7142857142857" customWidth="1"/>
+    <col min="3" max="3" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:6">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
@@ -2072,10 +2050,10 @@
       <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
@@ -2085,37 +2063,37 @@
         <v>10</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="B3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D4" s="1" t="s">
@@ -2125,17 +2103,17 @@
         <v>10</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D5" s="1" t="s">
@@ -2145,37 +2123,37 @@
         <v>10</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D7" s="1" t="s">
@@ -2185,17 +2163,17 @@
         <v>10</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D8" s="1" t="s">
@@ -2205,17 +2183,17 @@
         <v>10</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D9" s="1" t="s">
@@ -2225,17 +2203,17 @@
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D10" s="1" t="s">
@@ -2245,37 +2223,37 @@
         <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="1" t="s">
@@ -2285,17 +2263,17 @@
         <v>10</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
@@ -2305,17 +2283,17 @@
         <v>10</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="1" t="s">
@@ -2325,17 +2303,17 @@
         <v>10</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D15" s="1" t="s">
@@ -2345,17 +2323,17 @@
         <v>10</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D16" s="1" t="s">
@@ -2365,17 +2343,17 @@
         <v>10</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D17" s="1" t="s">
@@ -2385,17 +2363,17 @@
         <v>10</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D18" s="1" t="s">
@@ -2405,37 +2383,37 @@
         <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E19" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
         <v>46</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D20" s="1" t="s">
@@ -2445,17 +2423,17 @@
         <v>10</v>
       </c>
       <c r="F20" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D21" s="1" t="s">
@@ -2465,17 +2443,17 @@
         <v>10</v>
       </c>
       <c r="F21" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
         <v>50</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D22" s="1" t="s">
@@ -2485,17 +2463,17 @@
         <v>10</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
         <v>52</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D23" s="1" t="s">
@@ -2505,37 +2483,37 @@
         <v>10</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24" t="s">
         <v>54</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E24" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25" t="s">
         <v>56</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D25" s="1" t="s">
@@ -2545,17 +2523,17 @@
         <v>10</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26" t="s">
         <v>58</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D26" s="1" t="s">
@@ -2565,17 +2543,17 @@
         <v>10</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27" t="s">
         <v>60</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D27" s="1" t="s">
@@ -2585,37 +2563,37 @@
         <v>10</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28" t="s">
         <v>62</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E28" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29" t="s">
         <v>64</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D29" s="1" t="s">
@@ -2625,17 +2603,17 @@
         <v>10</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30" t="s">
         <v>66</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D30" s="1" t="s">
@@ -2645,17 +2623,17 @@
         <v>10</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31" t="s">
         <v>68</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D31" s="1" t="s">
@@ -2665,17 +2643,17 @@
         <v>10</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32" t="s">
         <v>70</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D32" s="1" t="s">
@@ -2685,17 +2663,17 @@
         <v>10</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="33" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33" t="s">
         <v>72</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D33" s="1" t="s">
@@ -2705,17 +2683,17 @@
         <v>10</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
       <c r="A34" t="s">
         <v>74</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D34" s="1" t="s">
@@ -2725,57 +2703,57 @@
         <v>10</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
       <c r="A35" t="s">
         <v>76</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E35" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
       <c r="A36" t="s">
         <v>78</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E36" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="37" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
       <c r="A37" t="s">
         <v>80</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D37" s="1" t="s">
@@ -2785,17 +2763,17 @@
         <v>10</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="38" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
       <c r="A38" t="s">
         <v>82</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D38" s="1" t="s">
@@ -2805,57 +2783,57 @@
         <v>10</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="39" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
       <c r="A39" t="s">
         <v>84</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E39" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
       <c r="A40" t="s">
         <v>86</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E40" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="41" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
       <c r="A41" t="s">
         <v>88</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D41" s="1" t="s">
@@ -2865,37 +2843,37 @@
         <v>10</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="42" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
       <c r="A42" t="s">
         <v>90</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E42" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F42" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="43" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
       <c r="A43" t="s">
         <v>92</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D43" s="1" t="s">
@@ -2905,17 +2883,17 @@
         <v>10</v>
       </c>
       <c r="F43" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="44" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
       <c r="A44" t="s">
         <v>94</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D44" s="1" t="s">
@@ -2925,17 +2903,17 @@
         <v>10</v>
       </c>
       <c r="F44" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="45" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
       <c r="A45" t="s">
         <v>96</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D45" s="1" t="s">
@@ -2945,17 +2923,17 @@
         <v>10</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="46" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
       <c r="A46" t="s">
         <v>98</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D46" s="1" t="s">
@@ -2965,17 +2943,17 @@
         <v>10</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="47" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
       <c r="A47" t="s">
         <v>100</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D47" s="1" t="s">
@@ -2985,17 +2963,17 @@
         <v>10</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="48" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
       <c r="A48" t="s">
         <v>102</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D48" s="1" t="s">
@@ -3005,17 +2983,17 @@
         <v>10</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="49" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
       <c r="A49" t="s">
         <v>104</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D49" s="1" t="s">
@@ -3025,37 +3003,37 @@
         <v>10</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="50" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
       <c r="A50" t="s">
         <v>106</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E50" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="51" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
       <c r="A51" t="s">
         <v>108</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C51" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D51" s="1" t="s">
@@ -3065,17 +3043,17 @@
         <v>10</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="52" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
       <c r="A52" t="s">
         <v>110</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B52" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C52" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D52" s="1" t="s">
@@ -3085,77 +3063,77 @@
         <v>10</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="53" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
       <c r="A53" t="s">
         <v>112</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B53" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C53" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E53" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="54" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
       <c r="A54" t="s">
         <v>114</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B54" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E54" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="55" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
       <c r="A55" t="s">
         <v>116</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B55" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E55" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="56" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
       <c r="A56" t="s">
         <v>118</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="B56" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D56" s="1" t="s">
@@ -3165,17 +3143,17 @@
         <v>10</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="57" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
       <c r="A57" t="s">
         <v>120</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B57" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D57" s="1" t="s">
@@ -3185,37 +3163,37 @@
         <v>10</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="58" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
       <c r="A58" t="s">
         <v>122</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B58" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C58" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E58" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="59" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
       <c r="A59" t="s">
         <v>124</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B59" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C59" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D59" s="1" t="s">
@@ -3225,17 +3203,17 @@
         <v>10</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="60" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
       <c r="A60" t="s">
         <v>126</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="B60" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C60" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D60" s="1" t="s">
@@ -3245,17 +3223,17 @@
         <v>10</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="61" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
       <c r="A61" t="s">
         <v>128</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="B61" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C61" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D61" s="1" t="s">
@@ -3265,17 +3243,17 @@
         <v>10</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="62" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
       <c r="A62" t="s">
         <v>130</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="B62" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C62" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D62" s="1" t="s">
@@ -3285,37 +3263,37 @@
         <v>10</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="63" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
       <c r="A63" t="s">
         <v>132</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="B63" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C63" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E63" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="64" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
       <c r="A64" t="s">
         <v>134</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="B64" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="C64" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D64" s="1" t="s">
@@ -3325,17 +3303,17 @@
         <v>10</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="65" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
       <c r="A65" t="s">
         <v>136</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="B65" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C65" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D65" s="1" t="s">
@@ -3345,17 +3323,17 @@
         <v>10</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="66" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
       <c r="A66" t="s">
         <v>138</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="B66" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C66" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D66" s="1" t="s">
@@ -3365,17 +3343,17 @@
         <v>10</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="67" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
       <c r="A67" t="s">
         <v>140</v>
       </c>
-      <c r="B67" s="2" t="s">
+      <c r="B67" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C67" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D67" s="1" t="s">
@@ -3385,17 +3363,17 @@
         <v>10</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="68" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
       <c r="A68" t="s">
         <v>142</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="B68" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="C68" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D68" s="1" t="s">
@@ -3405,17 +3383,17 @@
         <v>10</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="69" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
       <c r="A69" t="s">
         <v>144</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="B69" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="C69" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D69" s="1" t="s">
@@ -3425,17 +3403,17 @@
         <v>10</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="70" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
       <c r="A70" t="s">
         <v>146</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="B70" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="C70" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D70" s="1" t="s">
@@ -3445,17 +3423,17 @@
         <v>10</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="71" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
       <c r="A71" t="s">
         <v>148</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="B71" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="C71" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D71" s="1" t="s">
@@ -3465,17 +3443,17 @@
         <v>10</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="72" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
       <c r="A72" t="s">
         <v>150</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="B72" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="C72" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D72" s="1" t="s">
@@ -3485,17 +3463,17 @@
         <v>10</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="73" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
       <c r="A73" t="s">
         <v>152</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="B73" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="C73" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D73" s="1" t="s">
@@ -3505,17 +3483,17 @@
         <v>10</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="74" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
       <c r="A74" t="s">
         <v>154</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="B74" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="C74" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D74" s="1" t="s">
@@ -3525,17 +3503,17 @@
         <v>10</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="75" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
       <c r="A75" t="s">
         <v>156</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="B75" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C75" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D75" s="1" t="s">
@@ -3545,17 +3523,17 @@
         <v>10</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="76" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
       <c r="A76" t="s">
         <v>158</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="B76" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="C76" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D76" s="1" t="s">
@@ -3565,17 +3543,17 @@
         <v>10</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="77" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6">
       <c r="A77" t="s">
         <v>160</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="B77" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="C77" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D77" s="1" t="s">
@@ -3585,17 +3563,17 @@
         <v>10</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="78" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6">
       <c r="A78" t="s">
         <v>162</v>
       </c>
-      <c r="B78" s="2" t="s">
+      <c r="B78" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="C78" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D78" s="1" t="s">
@@ -3605,17 +3583,17 @@
         <v>10</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="79" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
       <c r="A79" t="s">
         <v>164</v>
       </c>
-      <c r="B79" s="2" t="s">
+      <c r="B79" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="C79" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D79" s="1" t="s">
@@ -3625,17 +3603,17 @@
         <v>10</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="80" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
       <c r="A80" t="s">
         <v>166</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="B80" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C80" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D80" s="1" t="s">
@@ -3645,37 +3623,37 @@
         <v>10</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="81" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
       <c r="A81" t="s">
         <v>168</v>
       </c>
-      <c r="B81" s="2" t="s">
+      <c r="B81" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="C81" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E81" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="82" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
       <c r="A82" t="s">
         <v>170</v>
       </c>
-      <c r="B82" s="2" t="s">
+      <c r="B82" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="C82" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D82" s="1" t="s">
@@ -3685,17 +3663,17 @@
         <v>10</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="83" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6">
       <c r="A83" t="s">
         <v>172</v>
       </c>
-      <c r="B83" s="2" t="s">
+      <c r="B83" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="C83" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D83" s="1" t="s">
@@ -3705,17 +3683,17 @@
         <v>10</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="84" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
       <c r="A84" t="s">
         <v>174</v>
       </c>
-      <c r="B84" s="2" t="s">
+      <c r="B84" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="C84" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D84" s="1" t="s">
@@ -3725,17 +3703,17 @@
         <v>10</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="85" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
       <c r="A85" t="s">
         <v>176</v>
       </c>
-      <c r="B85" s="2" t="s">
+      <c r="B85" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="C85" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D85" s="1" t="s">
@@ -3745,17 +3723,17 @@
         <v>10</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="86" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
       <c r="A86" t="s">
         <v>178</v>
       </c>
-      <c r="B86" s="2" t="s">
+      <c r="B86" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="C86" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D86" s="1" t="s">
@@ -3765,17 +3743,17 @@
         <v>10</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="87" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
       <c r="A87" t="s">
         <v>166</v>
       </c>
-      <c r="B87" s="2" t="s">
+      <c r="B87" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="C87" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D87" s="1" t="s">
@@ -3785,37 +3763,37 @@
         <v>10</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="88" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6">
       <c r="A88" t="s">
         <v>181</v>
       </c>
-      <c r="B88" s="2" t="s">
+      <c r="B88" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="C88" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E88" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="89" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6">
       <c r="A89" t="s">
         <v>183</v>
       </c>
-      <c r="B89" s="2" t="s">
+      <c r="B89" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="C89" s="1" t="s">
+      <c r="C89" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D89" s="1" t="s">
@@ -3825,17 +3803,17 @@
         <v>10</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="90" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6">
       <c r="A90" t="s">
         <v>185</v>
       </c>
-      <c r="B90" s="2" t="s">
+      <c r="B90" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="C90" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D90" s="1" t="s">
@@ -3845,17 +3823,17 @@
         <v>10</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="91" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6">
       <c r="A91" t="s">
         <v>187</v>
       </c>
-      <c r="B91" s="2" t="s">
+      <c r="B91" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="C91" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D91" s="1" t="s">
@@ -3865,17 +3843,17 @@
         <v>10</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="92" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6">
       <c r="A92" t="s">
         <v>189</v>
       </c>
-      <c r="B92" s="2" t="s">
+      <c r="B92" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="C92" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D92" s="1" t="s">
@@ -3885,17 +3863,17 @@
         <v>10</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="93" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
       <c r="A93" t="s">
         <v>191</v>
       </c>
-      <c r="B93" s="2" t="s">
+      <c r="B93" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="C93" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D93" s="1" t="s">
@@ -3905,17 +3883,17 @@
         <v>10</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="94" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6">
       <c r="A94" t="s">
         <v>193</v>
       </c>
-      <c r="B94" s="2" t="s">
+      <c r="B94" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="C94" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D94" s="1" t="s">
@@ -3925,17 +3903,17 @@
         <v>10</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="95" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6">
       <c r="A95" t="s">
         <v>195</v>
       </c>
-      <c r="B95" s="2" t="s">
+      <c r="B95" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="C95" s="1" t="s">
+      <c r="C95" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D95" s="1" t="s">
@@ -3945,17 +3923,17 @@
         <v>10</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="96" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6">
       <c r="A96" t="s">
         <v>197</v>
       </c>
-      <c r="B96" s="2" t="s">
+      <c r="B96" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="C96" s="1" t="s">
+      <c r="C96" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D96" s="1" t="s">
@@ -3965,17 +3943,17 @@
         <v>10</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="97" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6">
       <c r="A97" t="s">
         <v>199</v>
       </c>
-      <c r="B97" s="2" t="s">
+      <c r="B97" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="C97" s="1" t="s">
+      <c r="C97" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D97" s="1" t="s">
@@ -3985,17 +3963,17 @@
         <v>10</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="98" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
       <c r="A98" t="s">
         <v>201</v>
       </c>
-      <c r="B98" s="2" t="s">
+      <c r="B98" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="C98" s="1" t="s">
+      <c r="C98" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D98" s="1" t="s">
@@ -4005,17 +3983,17 @@
         <v>10</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="99" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6">
       <c r="A99" t="s">
         <v>203</v>
       </c>
-      <c r="B99" s="2" t="s">
+      <c r="B99" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="C99" s="1" t="s">
+      <c r="C99" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D99" s="1" t="s">
@@ -4025,17 +4003,17 @@
         <v>10</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="100" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
       <c r="A100" t="s">
         <v>205</v>
       </c>
-      <c r="B100" s="2" t="s">
+      <c r="B100" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="C100" s="1" t="s">
+      <c r="C100" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D100" s="1" t="s">
@@ -4045,17 +4023,17 @@
         <v>10</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="101" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6">
       <c r="A101" t="s">
         <v>207</v>
       </c>
-      <c r="B101" s="2" t="s">
+      <c r="B101" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="C101" s="1" t="s">
+      <c r="C101" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D101" s="1" t="s">
@@ -4065,17 +4043,17 @@
         <v>10</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="102" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6">
       <c r="A102" t="s">
         <v>209</v>
       </c>
-      <c r="B102" s="2" t="s">
+      <c r="B102" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="C102" s="1" t="s">
+      <c r="C102" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D102" s="1" t="s">
@@ -4085,17 +4063,17 @@
         <v>10</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="103" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6">
       <c r="A103" t="s">
         <v>211</v>
       </c>
-      <c r="B103" s="2" t="s">
+      <c r="B103" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C103" s="1" t="s">
+      <c r="C103" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D103" s="1" t="s">
@@ -4105,97 +4083,97 @@
         <v>10</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="104" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6">
       <c r="A104" t="s">
         <v>213</v>
       </c>
-      <c r="B104" s="2" t="s">
+      <c r="B104" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="C104" s="1" t="s">
+      <c r="C104" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E104" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="105" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6">
       <c r="A105" t="s">
         <v>215</v>
       </c>
-      <c r="B105" s="2" t="s">
+      <c r="B105" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="C105" s="1" t="s">
+      <c r="C105" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E105" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="106" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6">
       <c r="A106" t="s">
         <v>217</v>
       </c>
-      <c r="B106" s="2" t="s">
+      <c r="B106" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C106" s="1" t="s">
+      <c r="C106" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E106" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="107" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6">
       <c r="A107" t="s">
         <v>219</v>
       </c>
-      <c r="B107" s="2" t="s">
+      <c r="B107" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C107" s="1" t="s">
+      <c r="C107" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E107" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="108" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6">
       <c r="A108" t="s">
         <v>221</v>
       </c>
-      <c r="B108" s="2" t="s">
+      <c r="B108" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C108" s="1" t="s">
+      <c r="C108" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D108" s="1" t="s">
@@ -4205,17 +4183,17 @@
         <v>10</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="109" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
       <c r="A109" t="s">
         <v>223</v>
       </c>
-      <c r="B109" s="2" t="s">
+      <c r="B109" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C109" s="1" t="s">
+      <c r="C109" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D109" s="1" t="s">
@@ -4225,17 +4203,17 @@
         <v>10</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="110" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6">
       <c r="A110" t="s">
         <v>225</v>
       </c>
-      <c r="B110" s="2" t="s">
+      <c r="B110" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="C110" s="1" t="s">
+      <c r="C110" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D110" s="1" t="s">
@@ -4245,37 +4223,37 @@
         <v>10</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="111" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
       <c r="A111" t="s">
         <v>227</v>
       </c>
-      <c r="B111" s="2" t="s">
+      <c r="B111" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="C111" s="1" t="s">
+      <c r="C111" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D111" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E111" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="112" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6">
       <c r="A112" t="s">
         <v>229</v>
       </c>
-      <c r="B112" s="2" t="s">
+      <c r="B112" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="C112" s="1" t="s">
+      <c r="C112" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D112" s="1" t="s">
@@ -4285,17 +4263,17 @@
         <v>10</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="113" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
       <c r="A113" t="s">
         <v>231</v>
       </c>
-      <c r="B113" s="2" t="s">
+      <c r="B113" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="C113" s="1" t="s">
+      <c r="C113" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D113" s="1" t="s">
@@ -4305,17 +4283,17 @@
         <v>10</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="114" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
       <c r="A114" t="s">
         <v>233</v>
       </c>
-      <c r="B114" s="2" t="s">
+      <c r="B114" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="C114" s="1" t="s">
+      <c r="C114" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D114" s="1" t="s">
@@ -4325,77 +4303,77 @@
         <v>10</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="115" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6">
       <c r="A115" t="s">
         <v>235</v>
       </c>
-      <c r="B115" s="2" t="s">
+      <c r="B115" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="C115" s="1" t="s">
+      <c r="C115" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E115" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="116" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
       <c r="A116" t="s">
         <v>237</v>
       </c>
-      <c r="B116" s="2" t="s">
+      <c r="B116" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="C116" s="1" t="s">
+      <c r="C116" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E116" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="117" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6">
       <c r="A117" t="s">
         <v>239</v>
       </c>
-      <c r="B117" s="2" t="s">
+      <c r="B117" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="C117" s="1" t="s">
+      <c r="C117" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E117" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="118" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6">
       <c r="A118" t="s">
         <v>241</v>
       </c>
-      <c r="B118" s="2" t="s">
+      <c r="B118" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="C118" s="1" t="s">
+      <c r="C118" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D118" s="1" t="s">
@@ -4405,37 +4383,37 @@
         <v>10</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="119" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
       <c r="A119" t="s">
         <v>243</v>
       </c>
-      <c r="B119" s="2" t="s">
+      <c r="B119" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="C119" s="1" t="s">
+      <c r="C119" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E119" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="120" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6">
       <c r="A120" t="s">
         <v>245</v>
       </c>
-      <c r="B120" s="2" t="s">
+      <c r="B120" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="C120" s="1" t="s">
+      <c r="C120" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D120" s="1" t="s">
@@ -4445,17 +4423,17 @@
         <v>10</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="121" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6">
       <c r="A121" t="s">
         <v>247</v>
       </c>
-      <c r="B121" s="2" t="s">
+      <c r="B121" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="C121" s="1" t="s">
+      <c r="C121" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D121" s="1" t="s">
@@ -4465,17 +4443,17 @@
         <v>10</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="122" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6">
       <c r="A122" t="s">
         <v>249</v>
       </c>
-      <c r="B122" s="2" t="s">
+      <c r="B122" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="C122" s="1" t="s">
+      <c r="C122" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D122" s="1" t="s">
@@ -4485,77 +4463,77 @@
         <v>10</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="123" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6">
       <c r="A123" t="s">
         <v>251</v>
       </c>
-      <c r="B123" s="2" t="s">
+      <c r="B123" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="C123" s="1" t="s">
+      <c r="C123" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E123" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="124" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6">
       <c r="A124" t="s">
         <v>253</v>
       </c>
-      <c r="B124" s="2" t="s">
+      <c r="B124" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="C124" s="1" t="s">
+      <c r="C124" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D124" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E124" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="125" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6">
       <c r="A125" t="s">
         <v>255</v>
       </c>
-      <c r="B125" s="2" t="s">
+      <c r="B125" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="C125" s="1" t="s">
+      <c r="C125" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D125" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E125" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="126" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
       <c r="A126" t="s">
         <v>257</v>
       </c>
-      <c r="B126" s="2" t="s">
+      <c r="B126" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="C126" s="1" t="s">
+      <c r="C126" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D126" s="1" t="s">
@@ -4565,17 +4543,17 @@
         <v>10</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="127" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
       <c r="A127" t="s">
         <v>259</v>
       </c>
-      <c r="B127" s="2" t="s">
+      <c r="B127" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="C127" s="1" t="s">
+      <c r="C127" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D127" s="1" t="s">
@@ -4585,17 +4563,17 @@
         <v>10</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="128" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
       <c r="A128" t="s">
         <v>261</v>
       </c>
-      <c r="B128" s="2" t="s">
+      <c r="B128" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="C128" s="1" t="s">
+      <c r="C128" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D128" s="1" t="s">
@@ -4605,498 +4583,498 @@
         <v>10</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="129" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6">
       <c r="A129" t="s">
         <v>263</v>
       </c>
-      <c r="B129" s="2" t="s">
+      <c r="B129" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="C129" s="1" t="s">
+      <c r="C129" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D129" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E129" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="130" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6">
       <c r="A130" t="s">
         <v>265</v>
       </c>
-      <c r="B130" s="2" t="s">
+      <c r="B130" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="C130" s="1" t="s">
+      <c r="C130" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E130" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="131" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6">
       <c r="A131" t="s">
         <v>267</v>
       </c>
-      <c r="B131" s="2" t="s">
+      <c r="B131" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="C131" s="1" t="s">
+      <c r="C131" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D131" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E131" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="132" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6">
       <c r="A132" t="s">
         <v>269</v>
       </c>
-      <c r="B132" s="2" t="s">
+      <c r="B132" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="C132" s="1" t="s">
+      <c r="C132" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E132" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="133" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6">
       <c r="A133" t="s">
         <v>271</v>
       </c>
-      <c r="B133" s="2" t="s">
+      <c r="B133" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="C133" s="1" t="s">
+      <c r="C133" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E133" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="134" customFormat="1" spans="1:6">
       <c r="A134" t="s">
         <v>273</v>
       </c>
-      <c r="B134" s="2" t="s">
+      <c r="B134" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="C134" s="1" t="s">
+      <c r="C134" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E134" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="135" customFormat="1" spans="1:6">
       <c r="A135" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="B135" s="2" t="s">
+      <c r="B135" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C135" s="1" t="s">
+      <c r="C135" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D135" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E135" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="136" customFormat="1" spans="1:6">
       <c r="A136" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="B136" s="2" t="s">
+      <c r="B136" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="C136" s="1" t="s">
+      <c r="C136" s="4" t="s">
         <v>279</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E136" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="137" customFormat="1" spans="1:6">
       <c r="A137" t="s">
         <v>280</v>
       </c>
-      <c r="B137" s="2" t="s">
+      <c r="B137" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="C137" s="1" t="s">
+      <c r="C137" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D137" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E137" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="138" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
       <c r="A138" t="s">
         <v>282</v>
       </c>
-      <c r="B138" s="2" t="s">
+      <c r="B138" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="C138" s="1" t="s">
+      <c r="C138" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D138" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E138" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="139" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6">
       <c r="A139" t="s">
         <v>284</v>
       </c>
-      <c r="B139" s="2" t="s">
+      <c r="B139" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="C139" s="1" t="s">
+      <c r="C139" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D139" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E139" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="140" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6">
       <c r="A140" t="s">
         <v>286</v>
       </c>
-      <c r="B140" s="2" t="s">
+      <c r="B140" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="C140" s="1" t="s">
+      <c r="C140" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D140" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E140" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="141" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6">
       <c r="A141" t="s">
         <v>288</v>
       </c>
-      <c r="B141" s="2" t="s">
+      <c r="B141" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="C141" s="1" t="s">
+      <c r="C141" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D141" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E141" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="142" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
       <c r="A142" t="s">
         <v>290</v>
       </c>
-      <c r="B142" s="2" t="s">
+      <c r="B142" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="C142" s="1" t="s">
+      <c r="C142" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D142" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E142" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="143" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
       <c r="A143" t="s">
         <v>292</v>
       </c>
-      <c r="B143" s="2" t="s">
+      <c r="B143" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="C143" s="1" t="s">
+      <c r="C143" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D143" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E143" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="144" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6">
       <c r="A144" t="s">
         <v>294</v>
       </c>
-      <c r="B144" s="2" t="s">
+      <c r="B144" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="C144" s="1" t="s">
+      <c r="C144" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D144" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E144" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="145" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6">
       <c r="A145" t="s">
         <v>296</v>
       </c>
-      <c r="B145" s="2" t="s">
+      <c r="B145" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="C145" s="1" t="s">
+      <c r="C145" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D145" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E145" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="146" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6">
       <c r="A146" t="s">
         <v>298</v>
       </c>
-      <c r="B146" s="2" t="s">
+      <c r="B146" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="C146" s="1" t="s">
+      <c r="C146" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D146" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E146" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="147" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6">
       <c r="A147" t="s">
-        <v>280</v>
-      </c>
-      <c r="B147" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="C147" s="1" t="s">
+      <c r="B147" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="C147" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D147" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E147" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="148" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6">
       <c r="A148" t="s">
-        <v>301</v>
-      </c>
-      <c r="B148" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="C148" s="1" t="s">
+      <c r="B148" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="C148" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D148" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E148" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="149" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6">
       <c r="A149" t="s">
-        <v>303</v>
-      </c>
-      <c r="B149" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="C149" s="1" t="s">
+      <c r="B149" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="C149" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D149" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E149" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="150" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6">
       <c r="A150" t="s">
-        <v>305</v>
-      </c>
-      <c r="B150" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="C150" s="1" t="s">
+      <c r="B150" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C150" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D150" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E150" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="151" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6">
       <c r="A151" t="s">
-        <v>307</v>
-      </c>
-      <c r="B151" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="C151" s="1" t="s">
+      <c r="B151" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="C151" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D151" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E151" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="152" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6">
       <c r="A152" t="s">
-        <v>309</v>
-      </c>
-      <c r="B152" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="C152" s="3" t="s">
-        <v>8</v>
+        <v>310</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C152" s="4">
+        <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E152" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="153" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6">
       <c r="A153" t="s">
-        <v>310</v>
-      </c>
-      <c r="B153" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="C153" s="3" t="s">
-        <v>8</v>
+        <v>312</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C153" s="4">
+        <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
         <v>9</v>
@@ -5105,590 +5083,296 @@
         <v>10</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="154" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6">
       <c r="A154" t="s">
-        <v>311</v>
-      </c>
-      <c r="B154" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="C154" s="3" t="s">
-        <v>8</v>
+        <v>314</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C154" s="4">
+        <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E154" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="155" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6">
       <c r="A155" t="s">
-        <v>312</v>
-      </c>
-      <c r="B155" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="C155" s="3" t="s">
-        <v>8</v>
+        <v>316</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C155" s="4">
+        <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E155" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="156" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6">
       <c r="A156" t="s">
-        <v>313</v>
-      </c>
-      <c r="B156" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="C156" s="3" t="s">
-        <v>8</v>
+        <v>318</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C156" s="4">
+        <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E156" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="157" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6">
       <c r="A157" t="s">
-        <v>314</v>
-      </c>
-      <c r="B157" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="C157" s="3" t="s">
-        <v>8</v>
+        <v>320</v>
+      </c>
+      <c r="B157" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C157" s="4">
+        <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E157" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="158" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6">
       <c r="A158" t="s">
-        <v>315</v>
-      </c>
-      <c r="B158" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="C158" s="3" t="s">
-        <v>8</v>
+        <v>322</v>
+      </c>
+      <c r="B158" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="C158" s="4">
+        <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E158" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="159" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6">
       <c r="A159" t="s">
-        <v>316</v>
-      </c>
-      <c r="B159" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="C159" s="3" t="s">
-        <v>8</v>
+        <v>324</v>
+      </c>
+      <c r="B159" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="C159" s="4">
+        <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E159" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="160" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6">
       <c r="A160" t="s">
-        <v>317</v>
-      </c>
-      <c r="B160" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="C160" s="3" t="s">
-        <v>8</v>
+        <v>326</v>
+      </c>
+      <c r="B160" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C160" s="4">
+        <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E160" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="161" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
       <c r="A161" t="s">
-        <v>318</v>
-      </c>
-      <c r="B161" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="C161" s="3" t="s">
-        <v>8</v>
+        <v>328</v>
+      </c>
+      <c r="B161" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C161" s="4">
+        <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E161" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="162" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6">
       <c r="A162" t="s">
-        <v>319</v>
-      </c>
-      <c r="B162" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="C162" s="3" t="s">
-        <v>8</v>
+        <v>330</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C162" s="4">
+        <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E162" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="163" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6">
       <c r="A163" t="s">
-        <v>320</v>
-      </c>
-      <c r="B163" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="C163" s="3" t="s">
-        <v>8</v>
+        <v>332</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="C163" s="4">
+        <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E163" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="164" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
       <c r="A164" t="s">
-        <v>321</v>
-      </c>
-      <c r="B164" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="C164" s="3" t="s">
-        <v>8</v>
+        <v>334</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C164" s="4">
+        <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E164" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="165" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
       <c r="A165" t="s">
-        <v>322</v>
-      </c>
-      <c r="B165" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="C165" s="3" t="s">
-        <v>8</v>
+        <v>336</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="C165" s="4">
+        <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E165" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="166" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6">
       <c r="A166" t="s">
-        <v>323</v>
-      </c>
-      <c r="B166" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="C166" s="3" t="s">
-        <v>8</v>
+        <v>338</v>
+      </c>
+      <c r="B166" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C166" s="4">
+        <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E166" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="167" customFormat="1" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6">
       <c r="A167" t="s">
-        <v>325</v>
-      </c>
-      <c r="B167" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="C167" s="3" t="s">
-        <v>8</v>
+        <v>340</v>
+      </c>
+      <c r="B167" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C167" s="4">
+        <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E167" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="168" customFormat="1" spans="1:6">
-      <c r="A168" t="s">
-        <v>327</v>
-      </c>
-      <c r="B168" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="C168" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D168" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E168" t="s">
-        <v>13</v>
-      </c>
-      <c r="F168" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="169" customFormat="1" spans="1:6">
-      <c r="A169" t="s">
-        <v>329</v>
-      </c>
-      <c r="B169" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="C169" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E169" t="s">
-        <v>13</v>
-      </c>
-      <c r="F169" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="170" customFormat="1" ht="15" customHeight="1" spans="1:6">
-      <c r="A170" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="B170" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="C170" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D170" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E170" t="s">
-        <v>13</v>
-      </c>
-      <c r="F170" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="171" customFormat="1" spans="1:6">
-      <c r="A171" t="s">
-        <v>333</v>
-      </c>
-      <c r="B171" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="C171" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E171" t="s">
-        <v>13</v>
-      </c>
-      <c r="F171" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="172" customFormat="1" spans="1:6">
-      <c r="A172" t="s">
-        <v>335</v>
-      </c>
-      <c r="B172" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="C172" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E172" t="s">
-        <v>13</v>
-      </c>
-      <c r="F172" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="173" customFormat="1" spans="1:6">
-      <c r="A173" t="s">
-        <v>168</v>
-      </c>
-      <c r="B173" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="C173" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E173" t="s">
-        <v>13</v>
-      </c>
-      <c r="F173" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="174" customFormat="1" spans="1:6">
-      <c r="A174" t="s">
-        <v>338</v>
-      </c>
-      <c r="B174" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="C174" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E174" t="s">
-        <v>13</v>
-      </c>
-      <c r="F174" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="175" customFormat="1" spans="1:6">
-      <c r="A175" t="s">
-        <v>340</v>
-      </c>
-      <c r="B175" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="C175" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E175" t="s">
-        <v>13</v>
-      </c>
-      <c r="F175" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="176" customFormat="1" spans="1:6">
-      <c r="A176" t="s">
-        <v>310</v>
-      </c>
-      <c r="B176" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="C176" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D176" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E176" t="s">
-        <v>13</v>
-      </c>
-      <c r="F176" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="177" customFormat="1" spans="1:6">
-      <c r="A177" t="s">
-        <v>343</v>
-      </c>
-      <c r="B177" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="C177" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D177" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E177" t="s">
-        <v>13</v>
-      </c>
-      <c r="F177" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="178" customFormat="1" spans="1:6">
-      <c r="A178" t="s">
-        <v>345</v>
-      </c>
-      <c r="B178" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="C178" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E178" t="s">
-        <v>13</v>
-      </c>
-      <c r="F178" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="179" customFormat="1" spans="1:6">
-      <c r="A179" t="s">
-        <v>347</v>
-      </c>
-      <c r="B179" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="C179" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E179" t="s">
-        <v>13</v>
-      </c>
-      <c r="F179" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="180" customFormat="1" spans="1:6">
-      <c r="A180" t="s">
-        <v>349</v>
-      </c>
-      <c r="B180" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="C180" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E180" t="s">
-        <v>13</v>
-      </c>
-      <c r="F180" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="181" spans="1:6">
-      <c r="A181" t="s">
-        <v>351</v>
-      </c>
-      <c r="B181" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="C181" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D181" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E181" t="s">
-        <v>13</v>
-      </c>
-      <c r="F181" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="182" spans="1:6">
-      <c r="A182" t="s">
-        <v>353</v>
-      </c>
-      <c r="B182" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="C182" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D182" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E182" t="s">
-        <v>13</v>
-      </c>
-      <c r="F182" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F165" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
+  <conditionalFormatting sqref="B$1:B$1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>

--- a/testdata/listForExecution.xlsx
+++ b/testdata/listForExecution.xlsx
@@ -4,14 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12180"/>
+    <workbookView windowWidth="21864" windowHeight="9528"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$165</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -30,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="374">
   <si>
     <t>TestName</t>
   </si>
@@ -62,18 +59,18 @@
     <t>data</t>
   </si>
   <si>
+    <t>off</t>
+  </si>
+  <si>
+    <t>Product_Summary_Favourite_account_[WEB]</t>
+  </si>
+  <si>
+    <t>C70765</t>
+  </si>
+  <si>
     <t>on</t>
   </si>
   <si>
-    <t>off</t>
-  </si>
-  <si>
-    <t>Product_Summary_Favourite_account_[WEB]</t>
-  </si>
-  <si>
-    <t>C70765</t>
-  </si>
-  <si>
     <t>General-Dashboard-Quick_Links_[WEB]</t>
   </si>
   <si>
@@ -158,904 +155,1000 @@
     <t>C70779</t>
   </si>
   <si>
+    <t>General-Dashboard-Page_overview_[WEB]</t>
+  </si>
+  <si>
+    <t>C70780</t>
+  </si>
+  <si>
+    <t>Foreign_Current_Account_Product_Details_Account_Details_[WEB]</t>
+  </si>
+  <si>
+    <t>C70781</t>
+  </si>
+  <si>
+    <t>Current_Accounts-Transactions_Details-Create_Confirmation_[WEB]</t>
+  </si>
+  <si>
+    <t>C70782</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Transactions-Download_option_[WEB]</t>
+  </si>
+  <si>
+    <t>C70784</t>
+  </si>
+  <si>
+    <t>Foreign_Current_Accounts-Transactions-Filter_By_Type_[WEB]</t>
+  </si>
+  <si>
+    <t>C70785</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Account-Transactions-Filter_By_Type_[WEB]</t>
+  </si>
+  <si>
+    <t>C70786</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Transactions-Filter_By_Date-Predefined_Date_Range_[WEB]</t>
+  </si>
+  <si>
+    <t>C70787</t>
+  </si>
+  <si>
+    <t>Foreign_Current_Accounts-Multiple-Filter_Invalid_[WEB]</t>
+  </si>
+  <si>
+    <t>C70788</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts-Transactions-Download_option_[WEB]</t>
+  </si>
+  <si>
+    <t>C70789</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Multiple-Filter_Invalid_[WEB]</t>
+  </si>
+  <si>
+    <t>C70790</t>
+  </si>
+  <si>
+    <t>Foreign_Current_Account-Transactions-Filter_By_Date-Predefined_Date_Range_[WEB]</t>
+  </si>
+  <si>
+    <t>C70791</t>
+  </si>
+  <si>
+    <t>Manage_Products-Favorite_account_[WEB]</t>
+  </si>
+  <si>
+    <t>C70792</t>
+  </si>
+  <si>
+    <t>Manage_Products-Favorite_account-Removal_of_the_favorite_account_[WEB]</t>
+  </si>
+  <si>
+    <t>C70793</t>
+  </si>
+  <si>
+    <t>Manage_Products-Hide/Show_account_on_Product_List_[WEB]_1</t>
+  </si>
+  <si>
+    <t>C70794</t>
+  </si>
+  <si>
+    <t>Manage_Products-Hide/Show_account_on_Product_List_Invalid[WEB]_1</t>
+  </si>
+  <si>
+    <t>C70795</t>
+  </si>
+  <si>
+    <t>Manage_Products-Nickname_Product_Returning_To_Default_Name_[WEB]</t>
+  </si>
+  <si>
+    <t>C70796</t>
+  </si>
+  <si>
+    <t>Manage_Products-Nickname_Product_[WEB]_Invalid</t>
+  </si>
+  <si>
+    <t>C70797</t>
+  </si>
+  <si>
+    <t>Manage_Products-Nickname_Product_[WEB]</t>
+  </si>
+  <si>
+    <t>C70798</t>
+  </si>
+  <si>
+    <t>Products_Current_Accounts-Cheques_[WEB]</t>
+  </si>
+  <si>
+    <t>C70799</t>
+  </si>
+  <si>
+    <t>Products_Current_Accounts-Cheques-Filter_[WEB]</t>
+  </si>
+  <si>
+    <t>C70800</t>
+  </si>
+  <si>
+    <t>Products_Current_Accounts-Cheques-Input_Fields-invalid_[WEB]</t>
+  </si>
+  <si>
+    <t>C70801</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Transactions_List_[WEB]</t>
+  </si>
+  <si>
+    <t>C70802</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts-Transactions_List_[WEB]</t>
+  </si>
+  <si>
+    <t>C70803</t>
+  </si>
+  <si>
+    <t>Foreign_Current_Accounts-Transactions_List_select_Currency_[WEB]</t>
+  </si>
+  <si>
+    <t>C70804</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Details-Financial_Details_[WEB]</t>
+  </si>
+  <si>
+    <t>C70805</t>
+  </si>
+  <si>
+    <t>Credit_Cards-Header_Display_[WEB]</t>
+  </si>
+  <si>
+    <t>C70806</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Transactions_List_No_Transactions_[WEB]</t>
+  </si>
+  <si>
+    <t>C70807</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Transactions_Filter_By_Date-Date_Picker_[WEB]</t>
+  </si>
+  <si>
+    <t>C70808</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Transactions-Filter_By_Amount_[WEB]</t>
+  </si>
+  <si>
+    <t>C70809</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Transactions-Filter_By_Amount_Invalid_[WEB]</t>
+  </si>
+  <si>
+    <t>C70810</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts_Product_Details_Financial_Details_Is_Not_Visible_[WEB]</t>
+  </si>
+  <si>
+    <t>C70811</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts-Transactions_List_No_Transactions_[WEB]</t>
+  </si>
+  <si>
+    <t>C70812</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts-Transactions_Filter_By_Date-Date_Picker_[WEB]</t>
+  </si>
+  <si>
+    <t>C70813</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts-Transactions-Filter_By_Amount_[WEB]</t>
+  </si>
+  <si>
+    <t>C70814</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts-Transactions-Filter_By_Amount_Invalid_[WEB]</t>
+  </si>
+  <si>
+    <t>C70815</t>
+  </si>
+  <si>
+    <t>Savings_Accounts_Details-Financial_Details_[WEB]</t>
+  </si>
+  <si>
+    <t>C70816</t>
+  </si>
+  <si>
+    <t>Savings_Accounts_Details-Account_Details_[WEB]</t>
+  </si>
+  <si>
+    <t>C70817</t>
+  </si>
+  <si>
+    <t>Credit_Cards-Transactions_Filter_By_Date-Date_Picker_[WEB]</t>
+  </si>
+  <si>
+    <t>C70818</t>
+  </si>
+  <si>
+    <t>Credit_Cards-Transactions_Filter_By_Date-Date_Picker-invalid_[WEB]</t>
+  </si>
+  <si>
+    <t>C70819</t>
+  </si>
+  <si>
+    <t>Credit_Cards-Transactions_List_No_Transactions_[WEB]</t>
+  </si>
+  <si>
+    <t>C70820</t>
+  </si>
+  <si>
+    <t>Term_Deposits-Details_Account_Details_[WEB]</t>
+  </si>
+  <si>
+    <t>C70821</t>
+  </si>
+  <si>
+    <t>Product_Summary-Current_Foreign_Accounts_List_[WEB]</t>
+  </si>
+  <si>
+    <t>C70822</t>
+  </si>
+  <si>
+    <t>Product_Summary-Savings_Accounts_List_[WEB]</t>
+  </si>
+  <si>
+    <t>C70823</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Transactions_Filter-Invalid_[WEB]</t>
+  </si>
+  <si>
+    <t>C70824</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts-Transactions_Filter-Invalid_[WEB]</t>
+  </si>
+  <si>
+    <t>C70825</t>
+  </si>
+  <si>
+    <t>Payments_Recipient-Save_Recipient_[WEB]</t>
+  </si>
+  <si>
+    <t>C70826</t>
+  </si>
+  <si>
+    <t>Payments_Recipient-Delete_Recipient_[WEB]</t>
+  </si>
+  <si>
+    <t>C70827</t>
+  </si>
+  <si>
+    <t>Payments_Recipient-Update_Recipient_[WEB]</t>
+  </si>
+  <si>
+    <t>C70828</t>
+  </si>
+  <si>
+    <t>Payments_Recipient-Edit_Recipient-Invalid_[WEB]</t>
+  </si>
+  <si>
+    <t>C70829</t>
+  </si>
+  <si>
+    <t>Term_Deposits-Accounts_Details[WEB]</t>
+  </si>
+  <si>
+    <t>C70830</t>
+  </si>
+  <si>
+    <t>Product_Summary-Loan_List[WEB]</t>
+  </si>
+  <si>
+    <t>C70831</t>
+  </si>
+  <si>
+    <t>Foreign_Current_Accounts-Transactions-Search_[WEB]</t>
+  </si>
+  <si>
+    <t>C70832</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Transactions-Search_[WEB]</t>
+  </si>
+  <si>
+    <t>C70833</t>
+  </si>
+  <si>
+    <t>Payments_Recipient-Edit_Recipient-Edit_Account_number-invalid_[WEB]</t>
+  </si>
+  <si>
+    <t>C70834</t>
+  </si>
+  <si>
+    <t>Payments_Recipient-Update_Recipient-Update_Account_number_[WEB]</t>
+  </si>
+  <si>
+    <t>C70835</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments-Cancel_Button_[WEB]</t>
+  </si>
+  <si>
+    <t>C70836</t>
+  </si>
+  <si>
+    <t>Credit_Cards-Transactions-Download_Option_[WEB]</t>
+  </si>
+  <si>
+    <t>C70837</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments-Back_Button_[WEB]</t>
+  </si>
+  <si>
+    <t>C70838</t>
+  </si>
+  <si>
+    <t>Credit_Cards-Transactions_Filter_By_Type_[WEB]</t>
+  </si>
+  <si>
+    <t>C70839</t>
+  </si>
+  <si>
+    <t>Credit_Cards-Transactions_Filter_By_Amount_[WEB]</t>
+  </si>
+  <si>
+    <t>C70840</t>
+  </si>
+  <si>
+    <t>Credit_Cards-Transactions_Filter_By_Amount_invalid_[WEB]</t>
+  </si>
+  <si>
+    <t>C70841</t>
+  </si>
+  <si>
+    <t>Payments_Payments_Overview_Display_Options_For_The_Selected_Account_[WEB]</t>
+  </si>
+  <si>
+    <t>C70842</t>
+  </si>
+  <si>
+    <t>Credit_Cards-Transactions-Filter-Filter_By_Status_[WEB]</t>
+  </si>
+  <si>
+    <t>C70843</t>
+  </si>
+  <si>
+    <t>Credit_Cards-Transactions_Details_[WEB]</t>
+  </si>
+  <si>
+    <t>C70844</t>
+  </si>
+  <si>
+    <t>Domestic_Payments_Modify_Data_[WEB]</t>
+  </si>
+  <si>
+    <t>C70845</t>
+  </si>
+  <si>
+    <t>Domestic_Payments_In_Future_[WEB]</t>
+  </si>
+  <si>
+    <t>C70846</t>
+  </si>
+  <si>
+    <t>Credit_Cards-Transactions-Filter_Multiple_Filter_Invalid_[WEB]</t>
+  </si>
+  <si>
+    <t>C70847</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments-Create_New_Recipient_[WEB]</t>
+  </si>
+  <si>
+    <t>C70848</t>
+  </si>
+  <si>
+    <t>Payments-Own_Account_Transfer-Flow_Disruption_Cancel-Back_[WEB]</t>
+  </si>
+  <si>
+    <t>C70849</t>
+  </si>
+  <si>
+    <t>C70850</t>
+  </si>
+  <si>
+    <t>Payments-Payments_Archive-Filter_Payments_By_Date_[WEB]</t>
+  </si>
+  <si>
+    <t>C70851</t>
+  </si>
+  <si>
+    <t>Payments_Payments_Archive_Filter_Payments_By_Amount-Invalid_[WEB]</t>
+  </si>
+  <si>
+    <t>C70852</t>
+  </si>
+  <si>
+    <t>Payments_Payments_Archive_Filter_Payments_By_Status_[WEB]</t>
+  </si>
+  <si>
+    <t>C70853</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Details_[WEB]</t>
+  </si>
+  <si>
+    <t>C70854</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Header_[WEB]</t>
+  </si>
+  <si>
+    <t>C70855</t>
+  </si>
+  <si>
+    <t>Payments-Own_Account_Transfer-From_Savings_Account_RSD_[WEB]-To_Savings_Account</t>
+  </si>
+  <si>
+    <t>C70856</t>
+  </si>
+  <si>
+    <t>Payments-Own_Account_Transfer-From_Savings_Account_RSD_[WEB]-To_Current_Account</t>
+  </si>
+  <si>
+    <t>C70857</t>
+  </si>
+  <si>
+    <t>Payments-Own_Account_Transfer-From_Savings_Account_RSD_[WEB]-To_Charge_Card</t>
+  </si>
+  <si>
+    <t>C70858</t>
+  </si>
+  <si>
+    <t>Payments-Own_Account_Transfer-From_Current_Account_RSD_[WEB]-To_Current_Account</t>
+  </si>
+  <si>
+    <t>C70859</t>
+  </si>
+  <si>
+    <t>Payments-Own_Account_Transfer-From_Current_Account_RSD_[WEB]-To_Savings_Account</t>
+  </si>
+  <si>
+    <t>C70860</t>
+  </si>
+  <si>
+    <t>Payments-Own_Account_Transfer-From_Current_Account_RSD_[WEB]-To_Charge_Card</t>
+  </si>
+  <si>
+    <t>C70861</t>
+  </si>
+  <si>
+    <t>Payments-Own_Account_Transfer-Invalid_Account_Combination_[WEB]</t>
+  </si>
+  <si>
+    <t>C70862</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Annuity_Plan_[WEB]</t>
+  </si>
+  <si>
+    <t>C70863</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Annuity_Plan-Filter_[WEB]</t>
+  </si>
+  <si>
+    <t>C70864</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Payments_[WEB]</t>
+  </si>
+  <si>
+    <t>C70865</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Payments-Filter_[WEB]</t>
+  </si>
+  <si>
+    <t>C70866</t>
+  </si>
+  <si>
+    <t>Term_Deposits-Details-Financial_Details_[WEB]</t>
+  </si>
+  <si>
+    <t>C70867</t>
+  </si>
+  <si>
+    <t>Payments_Payments_Archive-Create_Confirmation_[WEB]</t>
+  </si>
+  <si>
+    <t>C70868</t>
+  </si>
+  <si>
+    <t>Authentication-Web_Login-Logout_[WEB]</t>
+  </si>
+  <si>
+    <t>C70869</t>
+  </si>
+  <si>
+    <t>Authentication-Web_Login-Login_With_OTP_[WEB]</t>
+  </si>
+  <si>
+    <t>C70870</t>
+  </si>
+  <si>
+    <t>Product_Summary-Current_Domestic_Accounts_List_[WEB]</t>
+  </si>
+  <si>
+    <t>C70871</t>
+  </si>
+  <si>
+    <t>Product_Summary-Term_Deposits_List_[WEB]</t>
+  </si>
+  <si>
+    <t>C70872</t>
+  </si>
+  <si>
+    <t>General-Login_Page_Elements-Overview_PreLogin_Page_[WEB]</t>
+  </si>
+  <si>
+    <t>C70873</t>
+  </si>
+  <si>
+    <t>General-Login_Page_Elements-Links_[WEB]</t>
+  </si>
+  <si>
+    <t>C70874</t>
+  </si>
+  <si>
+    <t>Authentication-Web_Login-Login_With_OTP-Invalid_OTP_[WEB]</t>
+  </si>
+  <si>
+    <t>C70875</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Annuity_Plan-Filter-invalid_[WEB]</t>
+  </si>
+  <si>
+    <t>C70876</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Payments-Filter-invalid_[WEB]</t>
+  </si>
+  <si>
+    <t>C70877</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments_[WEB]</t>
+  </si>
+  <si>
+    <t>C70878</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments-Confirmation_[WEB]</t>
+  </si>
+  <si>
+    <t>C70879</t>
+  </si>
+  <si>
+    <t>Payments-Payments_Overview_[WEB]</t>
+  </si>
+  <si>
+    <t>C70880</t>
+  </si>
+  <si>
+    <t>Product_Summary-Hide/Show_Product_on_Product_List_[WEB]_Credit_Cards</t>
+  </si>
+  <si>
+    <t>C70881</t>
+  </si>
+  <si>
+    <t>Payments_Recipient-Edit_Recipient_[WEB]</t>
+  </si>
+  <si>
+    <t>C70882</t>
+  </si>
+  <si>
+    <t>Current_Accounts_RSD-Statements-Download_[WEB]</t>
+  </si>
+  <si>
+    <t>C70883</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts-Statements-Download_[WEB]</t>
+  </si>
+  <si>
+    <t>C70884</t>
+  </si>
+  <si>
+    <t>Savings_Accounts-Statements-Download_[WEB]</t>
+  </si>
+  <si>
+    <t>C70885</t>
+  </si>
+  <si>
+    <t>Payments-Own_Account_Transfer-From_Current_Account_RSD_To_Current_Account_RSD_[WEB]</t>
+  </si>
+  <si>
+    <t>C70886</t>
+  </si>
+  <si>
+    <t>Payments-Own_Account_Transfer-To_Card_[WEB]-From_Current_Domestic_Account</t>
+  </si>
+  <si>
+    <t>C70887</t>
+  </si>
+  <si>
+    <t>Payments-Own_Account_Transfer-To_Card_[WEB]-From_Savings_Account</t>
+  </si>
+  <si>
+    <t>C70888</t>
+  </si>
+  <si>
+    <t>Current_Accounts_RSD-Statements-Empty_State_[WEB]</t>
+  </si>
+  <si>
+    <t>C70889</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts-Statements-Empty_State_[WEB]</t>
+  </si>
+  <si>
+    <t>C70890</t>
+  </si>
+  <si>
+    <t>Savings_Accounts-Statements-Empty_State_[WEB]</t>
+  </si>
+  <si>
+    <t>C70891</t>
+  </si>
+  <si>
+    <t>Savings_Accounts-Transactions_Details_[WEB]</t>
+  </si>
+  <si>
+    <t>C70892</t>
+  </si>
+  <si>
+    <t>Cards-Transactions_Details_[WEB]-Debit_Cards</t>
+  </si>
+  <si>
+    <t>C70893</t>
+  </si>
+  <si>
+    <t>Cards-Transactions_Details_[WEB]-Credit_Cards</t>
+  </si>
+  <si>
+    <t>C70894</t>
+  </si>
+  <si>
+    <t>Savings_accounts-Transactions_List_[WEB]</t>
+  </si>
+  <si>
+    <t>C70895</t>
+  </si>
+  <si>
+    <t>Payments-Upcoming_Payments-List_Of_Transactions_[WEB]</t>
+  </si>
+  <si>
+    <t>C70896</t>
+  </si>
+  <si>
+    <t>Payments-Upcoming_Payments-Cancel_Payments_[WEB]</t>
+  </si>
+  <si>
+    <t>C70897</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Details-Financial_Details_[WEB]</t>
+  </si>
+  <si>
+    <t>C70898</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Details-Account_Details_[WEB]</t>
+  </si>
+  <si>
+    <t>C70899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3, </t>
+  </si>
+  <si>
+    <t>Payments_Payments_Archive-Payments_List_[WEB]</t>
+  </si>
+  <si>
+    <t>C70900</t>
+  </si>
+  <si>
+    <t>Payments_Currency_Exchange_Pricelist_[WEB]-Overview</t>
+  </si>
+  <si>
+    <t>C70901</t>
+  </si>
+  <si>
+    <t>Saving_Accounts_Transactions_Download_Option_[WEB]</t>
+  </si>
+  <si>
+    <t>C70902</t>
+  </si>
+  <si>
+    <t>Payments_Own_Account_Transfer_To_Loan_[WEB]-From_Current_Domestic_Account</t>
+  </si>
+  <si>
+    <t>C70903</t>
+  </si>
+  <si>
+    <t>Payments_Own_Account_Transfer_From_Current_Foreign_Account_To_Current_Foreign_Account_[WEB]</t>
+  </si>
+  <si>
+    <t>C70904</t>
+  </si>
+  <si>
+    <t>Payments_Currency_Exchange_[WEB]-Buy_From_Payment</t>
+  </si>
+  <si>
+    <t>C70905</t>
+  </si>
+  <si>
+    <t>Payments_Currency_Exchange_[WEB]-Sell_From_Payment</t>
+  </si>
+  <si>
+    <t>C70906</t>
+  </si>
+  <si>
+    <t>Savings_Accounts_Transactions_Filter_By_Date_Date_Picker_[WEB]</t>
+  </si>
+  <si>
+    <t>C70907</t>
+  </si>
+  <si>
+    <t>Payments_Recipient_Template_List_[WEB]</t>
+  </si>
+  <si>
+    <t>C70908</t>
+  </si>
+  <si>
+    <t>Payments_Upcoming_Payments_Details_Of_Payments_Transaction_On_The_List_Of_Transaction_[WEB]</t>
+  </si>
+  <si>
+    <t>C70909</t>
+  </si>
+  <si>
+    <t>C70910</t>
+  </si>
+  <si>
+    <t>Payments_Payments_Archive_Payments_Details_[WEB]</t>
+  </si>
+  <si>
+    <t>C70911</t>
+  </si>
+  <si>
+    <t>Current_Accounts_RSD_Statemants_List_[WEB]</t>
+  </si>
+  <si>
+    <t>C70912</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts_Statemants_List_[WEB]</t>
+  </si>
+  <si>
+    <t>C70913</t>
+  </si>
+  <si>
+    <t>Saving_Accounts_Accounts_Statemants_List_[WEB]</t>
+  </si>
+  <si>
+    <t>C70914</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_Internal_Urgent_Payment_[WEB]</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_Internal_Non_Urgent_Payment_[WEB]</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_External_Urgent_Payment_No_Model_[WEB]</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_External_Urgent_Payment_Model11_Invalid_Bez_Poziva_Na_Broj_[WEB]</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_External_Non_Urgent_Payment_Model11_[WEB]</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_External_Urgent_Payment_Model97_Invalid_Bez_Poziva_Na_Broj_[WEB]</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_External_Non_Urgent_Payment_Model97_[WEB]</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_Budzetski_Urgent_Payment_Purpose_Code_289_Invalid_[WEB]</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_Budzetski_Urgent_Payment_Without_Reference_Number_Invalid_[WEB]</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_Budzetski_Urgent_Payment_Model97_[WEB]</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_Budzetski_Non_Urgent_Payment_Model97_[WEB]</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_External_Urgent_Payment_Model97_[WEB]</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_External_Urgent_Payment_Model11_[WEB]</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_External_Non_Urgent_Payment_No_Model_[WEB]</t>
+  </si>
+  <si>
+    <t>Payments_Own_Account_Transfer_To_Loan_[WEB]-From_Savings_Account</t>
+  </si>
+  <si>
+    <t>C70915</t>
+  </si>
+  <si>
+    <t>Credit_Cards_Details_Card_Details_[WEB]</t>
+  </si>
+  <si>
+    <t>C70916</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments_[MOB_ANDROID]-Internal_Non_Urgent_Payment</t>
+  </si>
+  <si>
+    <t>C70917</t>
+  </si>
+  <si>
+    <t>Payments_Recipient_Last_5_Payments_Of_Recipient_[WEB]-View_And_Repeat</t>
+  </si>
+  <si>
+    <t>C70918</t>
+  </si>
+  <si>
+    <t>Payments_Payments_Arhive_Resubmit_Payments_From_Past_Payment_List_[WEB]-Internal_Transfer</t>
+  </si>
+  <si>
+    <t>C70919</t>
+  </si>
+  <si>
+    <t>Payments_Payments_Arhive_Resubmit_Payments_From_Past_Payment_List_[WEB]-Domestic_Payment</t>
+  </si>
+  <si>
+    <t>C70920</t>
+  </si>
+  <si>
+    <t>Payments_Payments_Arhive_Resubmit_Payments_From_Past_Payment_List_[WEB]-Prenesi</t>
+  </si>
+  <si>
+    <t>C70921</t>
+  </si>
+  <si>
+    <t>C70922</t>
+  </si>
+  <si>
+    <t>Payments_Specific_Payment_Credit_Card_Repayment_[WEB]-From_Current_Domestic_Account</t>
+  </si>
+  <si>
+    <t>C70923</t>
+  </si>
+  <si>
+    <t>Payments_Specific_Payment_Credit_Card_Repayment_[WEB]-From_Savings_Account</t>
+  </si>
+  <si>
+    <t>C70924</t>
+  </si>
+  <si>
+    <t>C70925</t>
+  </si>
+  <si>
     <t>General_Dashboard_Page_overview_[WEB]</t>
   </si>
   <si>
-    <t>C70780</t>
-  </si>
-  <si>
-    <t>Foreign_Current_Account_Product_Details_Account_Details_[WEB]</t>
-  </si>
-  <si>
-    <t>C70781</t>
-  </si>
-  <si>
-    <t>Current_Accounts-Transactions_Details-Create_Confirmation_[WEB]</t>
-  </si>
-  <si>
-    <t>C70782</t>
-  </si>
-  <si>
-    <t>Current_Domestic_Accounts-Transactions-Download_option_[WEB]</t>
-  </si>
-  <si>
-    <t>C70784</t>
-  </si>
-  <si>
-    <t>Foreign_Current_Accounts-Transactions-Filter_By_Type_[WEB]</t>
-  </si>
-  <si>
-    <t>C70785</t>
-  </si>
-  <si>
-    <t>Current_Domestic_Account-Transactions-Filter_By_Type_[WEB]</t>
-  </si>
-  <si>
-    <t>C70786</t>
-  </si>
-  <si>
-    <t>Current_Domestic_Accounts-Transactions-Filter_By_Date-Predefined_Date_Range_[WEB]</t>
-  </si>
-  <si>
-    <t>C70787</t>
-  </si>
-  <si>
-    <t>Foreign_Current_Accounts-Multiple-Filter_Invalid_[WEB]</t>
-  </si>
-  <si>
-    <t>C70788</t>
-  </si>
-  <si>
-    <t>Current_Foreign_Accounts-Transactions-Download_option_[WEB]</t>
-  </si>
-  <si>
-    <t>C70789</t>
-  </si>
-  <si>
-    <t>Current_Domestic_Accounts-Multiple-Filter_Invalid_[WEB]</t>
-  </si>
-  <si>
-    <t>C70790</t>
-  </si>
-  <si>
-    <t>Foreign_Current_Account-Transactions-Filter_By_Date-Predefined_Date_Range_[WEB]</t>
-  </si>
-  <si>
-    <t>C70791</t>
-  </si>
-  <si>
-    <t>Manage_Products-Favorite_account_[WEB]</t>
-  </si>
-  <si>
-    <t>C70792</t>
-  </si>
-  <si>
-    <t>Manage_Products-Favorite_account-Removal_of_the_favorite_account_[WEB]</t>
-  </si>
-  <si>
-    <t>C70793</t>
-  </si>
-  <si>
-    <t>Manage_Products-Hide/Show_account_on_Product_List_[WEB]_1</t>
-  </si>
-  <si>
-    <t>C70794</t>
-  </si>
-  <si>
-    <t>Manage_Products-Hide/Show_account_on_Product_List_Invalid[WEB]_1</t>
-  </si>
-  <si>
-    <t>C70795</t>
-  </si>
-  <si>
-    <t>Manage_Products-Nickname_Product_Returning_To_Default_Name_[WEB]</t>
-  </si>
-  <si>
-    <t>C70796</t>
-  </si>
-  <si>
-    <t>Manage_Products-Nickname_Product_[WEB]_Invalid</t>
-  </si>
-  <si>
-    <t>C70797</t>
-  </si>
-  <si>
-    <t>Manage_Products-Nickname_Product_[WEB]</t>
-  </si>
-  <si>
-    <t>C70798</t>
-  </si>
-  <si>
-    <t>Products_Current_Accounts-Cheques_[WEB]</t>
-  </si>
-  <si>
-    <t>C70799</t>
-  </si>
-  <si>
-    <t>Products_Current_Accounts-Cheques-Filter_[WEB]</t>
-  </si>
-  <si>
-    <t>C70800</t>
-  </si>
-  <si>
-    <t>Products_Current_Accounts-Cheques-Input_Fields-invalid_[WEB]</t>
-  </si>
-  <si>
-    <t>C70801</t>
-  </si>
-  <si>
-    <t>Current_Domestic_Accounts-Transactions_List_[WEB]</t>
-  </si>
-  <si>
-    <t>C70802</t>
-  </si>
-  <si>
-    <t>Current_Foreign_Accounts-Transactions_List_[WEB]</t>
-  </si>
-  <si>
-    <t>C70803</t>
-  </si>
-  <si>
-    <t>Foreign_Current_Accounts-Transactions_List_select_Currency_[WEB]</t>
-  </si>
-  <si>
-    <t>C70804</t>
-  </si>
-  <si>
-    <t>Current_Domestic_Accounts-Details-Financial_Details_[WEB]</t>
-  </si>
-  <si>
-    <t>C70805</t>
-  </si>
-  <si>
-    <t>Credit_Cards-Header_Display_[WEB]</t>
-  </si>
-  <si>
-    <t>C70806</t>
-  </si>
-  <si>
-    <t>Current_Domestic_Accounts-Transactions_List_No_Transactions_[WEB]</t>
-  </si>
-  <si>
-    <t>C70807</t>
-  </si>
-  <si>
-    <t>Current_Domestic_Accounts-Transactions_Filter_By_Date-Date_Picker_[WEB]</t>
-  </si>
-  <si>
-    <t>C70808</t>
-  </si>
-  <si>
-    <t>Current_Domestic_Accounts-Transactions-Filter_By_Amount_[WEB]</t>
-  </si>
-  <si>
-    <t>C70809</t>
-  </si>
-  <si>
-    <t>Current_Domestic_Accounts-Transactions-Filter_By_Amount_Invalid_[WEB]</t>
-  </si>
-  <si>
-    <t>C70810</t>
-  </si>
-  <si>
-    <t>Current_Foreign_Accounts_Product_Details_Financial_Details_Is_Not_Visible_[WEB]</t>
-  </si>
-  <si>
-    <t>C70811</t>
-  </si>
-  <si>
-    <t>Current_Foreign_Accounts-Transactions_List_No_Transactions_[WEB]</t>
-  </si>
-  <si>
-    <t>C70812</t>
-  </si>
-  <si>
-    <t>Current_Foreign_Accounts-Transactions_Filter_By_Date-Date_Picker_[WEB]</t>
-  </si>
-  <si>
-    <t>C70813</t>
-  </si>
-  <si>
-    <t>Current_Foreign_Accounts-Transactions-Filter_By_Amount_[WEB]</t>
-  </si>
-  <si>
-    <t>C70814</t>
-  </si>
-  <si>
-    <t>Current_Foreign_Accounts-Transactions-Filter_By_Amount_Invalid_[WEB]</t>
-  </si>
-  <si>
-    <t>C70815</t>
-  </si>
-  <si>
-    <t>Savings_Accounts_Details-Financial_Details_[WEB]</t>
-  </si>
-  <si>
-    <t>C70816</t>
-  </si>
-  <si>
-    <t>Savings_Accounts_Details-Account_Details_[WEB]</t>
-  </si>
-  <si>
-    <t>C70817</t>
-  </si>
-  <si>
-    <t>Credit_Cards-Transactions_Filter_By_Date-Date_Picker_[WEB]</t>
-  </si>
-  <si>
-    <t>C70818</t>
-  </si>
-  <si>
-    <t>Credit_Cards-Transactions_Filter_By_Date-Date_Picker-invalid_[WEB]</t>
-  </si>
-  <si>
-    <t>C70819</t>
-  </si>
-  <si>
-    <t>Credit_Cards-Transactions_List_No_Transactions_[WEB]</t>
-  </si>
-  <si>
-    <t>C70820</t>
-  </si>
-  <si>
-    <t>Term_Deposits-Details_Account_Details_[WEB]</t>
-  </si>
-  <si>
-    <t>C70821</t>
-  </si>
-  <si>
-    <t>Product_Summary-Current_Foreign_Accounts_List_[WEB]</t>
-  </si>
-  <si>
-    <t>C70822</t>
-  </si>
-  <si>
-    <t>Product_Summary-Savings_Accounts_List_[WEB]</t>
-  </si>
-  <si>
-    <t>C70823</t>
-  </si>
-  <si>
-    <t>Current_Domestic_Accounts-Transactions_Filter-Invalid_[WEB]</t>
-  </si>
-  <si>
-    <t>C70824</t>
-  </si>
-  <si>
-    <t>Current_Foreign_Accounts-Transactions_Filter-Invalid_[WEB]</t>
-  </si>
-  <si>
-    <t>C70825</t>
-  </si>
-  <si>
-    <t>Payments_Recipient-Save_Recipient_[WEB]</t>
-  </si>
-  <si>
-    <t>C70826</t>
-  </si>
-  <si>
-    <t>Payments_Recipient-Delete_Recipient_[WEB]</t>
-  </si>
-  <si>
-    <t>C70827</t>
-  </si>
-  <si>
-    <t>Payments_Recipient-Update_Recipient_[WEB]</t>
-  </si>
-  <si>
-    <t>C70828</t>
-  </si>
-  <si>
-    <t>Payments_Recipient-Edit_Recipient-Invalid_[WEB]</t>
-  </si>
-  <si>
-    <t>C70829</t>
-  </si>
-  <si>
-    <t>Term_Deposits-Accounts_Details[WEB]</t>
-  </si>
-  <si>
-    <t>C70830</t>
-  </si>
-  <si>
-    <t>Product_Summary-Loan_List[WEB]</t>
-  </si>
-  <si>
-    <t>C70831</t>
-  </si>
-  <si>
-    <t>Foreign_Current_Accounts-Transactions-Search_[WEB]</t>
-  </si>
-  <si>
-    <t>C70832</t>
-  </si>
-  <si>
-    <t>Current_Domestic_Accounts-Transactions-Search_[WEB]</t>
-  </si>
-  <si>
-    <t>C70833</t>
-  </si>
-  <si>
-    <t>Payments_Recipient-Edit_Recipient-Edit_Account_number-invalid_[WEB]</t>
-  </si>
-  <si>
-    <t>C70834</t>
-  </si>
-  <si>
-    <t>Payments_Recipient-Update_Recipient-Update_Account_number_[WEB]</t>
-  </si>
-  <si>
-    <t>C70835</t>
-  </si>
-  <si>
-    <t>Payments-Domestic_Payments-Cancel_Button_[WEB]</t>
-  </si>
-  <si>
-    <t>C70836</t>
-  </si>
-  <si>
-    <t>Credit_Cards-Transactions-Download_Option_[WEB]</t>
-  </si>
-  <si>
-    <t>C70837</t>
-  </si>
-  <si>
-    <t>Payments-Domestic_Payments-Back_Button_[WEB]</t>
-  </si>
-  <si>
-    <t>C70838</t>
-  </si>
-  <si>
-    <t>Credit_Cards-Transactions_Filter_By_Type_[WEB]</t>
-  </si>
-  <si>
-    <t>C70839</t>
-  </si>
-  <si>
-    <t>Credit_Cards-Transactions_Filter_By_Amount_[WEB]</t>
-  </si>
-  <si>
-    <t>C70840</t>
-  </si>
-  <si>
-    <t>Credit_Cards-Transactions_Filter_By_Amount_invalid_[WEB]</t>
-  </si>
-  <si>
-    <t>C70841</t>
-  </si>
-  <si>
-    <t>Payments_Payments_Overview_Display_Options_For_The_Selected_Account_[WEB]</t>
-  </si>
-  <si>
-    <t>C70842</t>
-  </si>
-  <si>
-    <t>Credit_Cards-Transactions-Filter-Filter_By_Status_[WEB]</t>
-  </si>
-  <si>
-    <t>C70843</t>
-  </si>
-  <si>
-    <t>Credit_Cards-Transactions_Details_[WEB]</t>
-  </si>
-  <si>
-    <t>C70844</t>
-  </si>
-  <si>
-    <t>Domestic_Payments_Modify_Data_[WEB]</t>
-  </si>
-  <si>
-    <t>C70845</t>
-  </si>
-  <si>
-    <t>Domestic_Payments_In_Future_[WEB]</t>
-  </si>
-  <si>
-    <t>C70846</t>
-  </si>
-  <si>
-    <t>Credit_Cards-Transactions-Filter_Multiple_Filter_Invalid_[WEB]</t>
-  </si>
-  <si>
-    <t>C70847</t>
-  </si>
-  <si>
-    <t>Payments-Domestic_Payments-Create_New_Recipient_[WEB]</t>
-  </si>
-  <si>
-    <t>C70848</t>
-  </si>
-  <si>
-    <t>Payments-Own_Account_Transfer-Flow_Disruption_Cancel-Back_[WEB]</t>
-  </si>
-  <si>
-    <t>C70849</t>
-  </si>
-  <si>
-    <t>C70850</t>
-  </si>
-  <si>
-    <t>Payments-Payments_Archive-Filter_Payments_By_Date_[WEB]</t>
-  </si>
-  <si>
-    <t>C70851</t>
-  </si>
-  <si>
-    <t>Payments_Payments_Archive_Filter_Payments_By_Amount-Invalid_[WEB]</t>
-  </si>
-  <si>
-    <t>C70852</t>
-  </si>
-  <si>
-    <t>Payments_Payments_Archive_Filter_Payments_By_Status_[WEB]</t>
-  </si>
-  <si>
-    <t>C70853</t>
-  </si>
-  <si>
-    <t>Loan_Accounts-Details_[WEB]</t>
-  </si>
-  <si>
-    <t>C70854</t>
-  </si>
-  <si>
-    <t>Loan_Accounts-Header_[WEB]</t>
-  </si>
-  <si>
-    <t>C70855</t>
-  </si>
-  <si>
-    <t>Payments-Own_Account_Transfer-From_Savings_Account_RSD_[WEB]-To_Savings_Account</t>
-  </si>
-  <si>
-    <t>C70856</t>
-  </si>
-  <si>
-    <t>Payments-Own_Account_Transfer-From_Savings_Account_RSD_[WEB]-To_Current_Account</t>
-  </si>
-  <si>
-    <t>C70857</t>
-  </si>
-  <si>
-    <t>Payments-Own_Account_Transfer-From_Savings_Account_RSD_[WEB]-To_Charge_Card</t>
-  </si>
-  <si>
-    <t>C70858</t>
-  </si>
-  <si>
-    <t>Payments-Own_Account_Transfer-From_Current_Account_RSD_[WEB]-To_Current_Account</t>
-  </si>
-  <si>
-    <t>C70859</t>
-  </si>
-  <si>
-    <t>Payments-Own_Account_Transfer-From_Current_Account_RSD_[WEB]-To_Savings_Account</t>
-  </si>
-  <si>
-    <t>C70860</t>
-  </si>
-  <si>
-    <t>Payments-Own_Account_Transfer-From_Current_Account_RSD_[WEB]-To_Charge_Card</t>
-  </si>
-  <si>
-    <t>C70861</t>
-  </si>
-  <si>
-    <t>Payments-Own_Account_Transfer-Invalid_Account_Combination_[WEB]</t>
-  </si>
-  <si>
-    <t>C70862</t>
-  </si>
-  <si>
-    <t>Loan_Accounts-Annuity_Plan_[WEB]</t>
-  </si>
-  <si>
-    <t>C70863</t>
-  </si>
-  <si>
-    <t>Loan_Accounts-Annuity_Plan-Filter_[WEB]</t>
-  </si>
-  <si>
-    <t>C70864</t>
-  </si>
-  <si>
-    <t>Loan_Accounts-Payments_[WEB]</t>
-  </si>
-  <si>
-    <t>C70865</t>
-  </si>
-  <si>
-    <t>Loan_Accounts-Payments-Filter_[WEB]</t>
-  </si>
-  <si>
-    <t>C70866</t>
-  </si>
-  <si>
-    <t>Term_Deposits-Details-Financial_Details_[WEB]</t>
-  </si>
-  <si>
-    <t>C70867</t>
-  </si>
-  <si>
-    <t>Payments_Payments_Archive-Create_Confirmation_[WEB]</t>
-  </si>
-  <si>
-    <t>C70868</t>
-  </si>
-  <si>
-    <t>Authentication-Web_Login-Logout_[WEB]</t>
-  </si>
-  <si>
-    <t>C70869</t>
-  </si>
-  <si>
-    <t>Authentication-Web_Login-Login_With_OTP_[WEB]</t>
-  </si>
-  <si>
-    <t>C70870</t>
-  </si>
-  <si>
-    <t>Product_Summary-Current_Domestic_Accounts_List_[WEB]</t>
-  </si>
-  <si>
-    <t>C70871</t>
-  </si>
-  <si>
-    <t>Product_Summary-Term_Deposits_List_[WEB]</t>
-  </si>
-  <si>
-    <t>C70872</t>
-  </si>
-  <si>
-    <t>General-Login_Page_Elements-Overview_PreLogin_Page_[WEB]</t>
-  </si>
-  <si>
-    <t>C70873</t>
-  </si>
-  <si>
-    <t>General-Login_Page_Elements-Links_[WEB]</t>
-  </si>
-  <si>
-    <t>C70874</t>
-  </si>
-  <si>
-    <t>Authentication-Web_Login-Login_With_OTP-Invalid_OTP_[WEB]</t>
-  </si>
-  <si>
-    <t>C70875</t>
-  </si>
-  <si>
-    <t>Loan_Accounts-Annuity_Plan-Filter-invalid_[WEB]</t>
-  </si>
-  <si>
-    <t>C70876</t>
-  </si>
-  <si>
-    <t>Loan_Accounts-Payments-Filter-invalid_[WEB]</t>
-  </si>
-  <si>
-    <t>C70877</t>
-  </si>
-  <si>
-    <t>Payments-Domestic_Payments_[WEB]</t>
-  </si>
-  <si>
-    <t>C70878</t>
-  </si>
-  <si>
-    <t>Payments-Domestic_Payments-Confirmation_[WEB]</t>
-  </si>
-  <si>
-    <t>C70879</t>
-  </si>
-  <si>
-    <t>Payments-Payments_Overview_[WEB]</t>
-  </si>
-  <si>
-    <t>C70880</t>
-  </si>
-  <si>
-    <t>Product_Summary-Hide/Show_Product_on_Product_List_[WEB]_Credit_Cards</t>
-  </si>
-  <si>
-    <t>C70881</t>
-  </si>
-  <si>
-    <t>Payments_Recipient-Edit_Recipient_[WEB]</t>
-  </si>
-  <si>
-    <t>C70882</t>
-  </si>
-  <si>
-    <t>Current_Accounts_RSD-Statements-Download_[WEB]</t>
-  </si>
-  <si>
-    <t>C70883</t>
-  </si>
-  <si>
-    <t>Current_Foreign_Accounts-Statements-Download_[WEB]</t>
-  </si>
-  <si>
-    <t>C70884</t>
-  </si>
-  <si>
-    <t>Savings_Accounts-Statements-Download_[WEB]</t>
-  </si>
-  <si>
-    <t>C70885</t>
-  </si>
-  <si>
-    <t>Payments-Own_Account_Transfer-From_Current_Account_RSD_To_Current_Account_RSD_[WEB]</t>
-  </si>
-  <si>
-    <t>C70886</t>
-  </si>
-  <si>
-    <t>Payments-Own_Account_Transfer-To_Card_[WEB]-From_Current_Domestic_Account</t>
-  </si>
-  <si>
-    <t>C70887</t>
-  </si>
-  <si>
-    <t>Payments-Own_Account_Transfer-To_Card_[WEB]-From_Savings_Account</t>
-  </si>
-  <si>
-    <t>C70888</t>
-  </si>
-  <si>
-    <t>Current_Accounts_RSD-Statements-Empty_State_[WEB]</t>
-  </si>
-  <si>
-    <t>C70889</t>
-  </si>
-  <si>
-    <t>Current_Foreign_Accounts-Statements-Empty_State_[WEB]</t>
-  </si>
-  <si>
-    <t>C70890</t>
-  </si>
-  <si>
-    <t>Savings_Accounts-Statements-Empty_State_[WEB]</t>
-  </si>
-  <si>
-    <t>C70891</t>
-  </si>
-  <si>
-    <t>Savings_Accounts-Transactions_Details_[WEB]</t>
-  </si>
-  <si>
-    <t>C70892</t>
-  </si>
-  <si>
-    <t>Cards-Transactions_Details_[WEB]-Debit_Cards</t>
-  </si>
-  <si>
-    <t>C70893</t>
-  </si>
-  <si>
-    <t>Cards-Transactions_Details_[WEB]-Credit_Cards</t>
-  </si>
-  <si>
-    <t>C70894</t>
-  </si>
-  <si>
-    <t>Savings_accounts-Transactions_List_[WEB]</t>
-  </si>
-  <si>
-    <t>C70895</t>
-  </si>
-  <si>
-    <t>Payments-Upcoming_Payments-List_Of_Transactions_[WEB]</t>
-  </si>
-  <si>
-    <t>C70896</t>
-  </si>
-  <si>
-    <t>Payments-Upcoming_Payments-Cancel_Payments_[WEB]</t>
-  </si>
-  <si>
-    <t>C70897</t>
-  </si>
-  <si>
-    <t>Loan_Accounts-Details-Financial_Details_[WEB]</t>
-  </si>
-  <si>
-    <t>C70898</t>
-  </si>
-  <si>
-    <t>Loan_Accounts-Details-Account_Details_[WEB]</t>
-  </si>
-  <si>
-    <t>C70899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3, </t>
-  </si>
-  <si>
-    <t>Payments_Payments_Archive-Payments_List_[WEB]</t>
-  </si>
-  <si>
-    <t>C70900</t>
-  </si>
-  <si>
-    <t>Payments_Domestic_Payments_Internal_Urgent_Payment_[WEB]</t>
-  </si>
-  <si>
-    <t>C70901</t>
-  </si>
-  <si>
-    <t>Payments_Domestic_Payments_Internal_Non_Urgent_Payment_[WEB]</t>
-  </si>
-  <si>
-    <t>C70902</t>
-  </si>
-  <si>
-    <t>Payments_Domestic_Payments_External_Urgent_Payment_No_Model_[WEB]</t>
-  </si>
-  <si>
-    <t>C70903</t>
-  </si>
-  <si>
-    <t>Payments_Domestic_Payments_External_Urgent_Payment_Model11_Invalid_Bez_Poziva_Na_Broj_[WEB]</t>
-  </si>
-  <si>
-    <t>C70904</t>
-  </si>
-  <si>
-    <t>Payments_Domestic_Payments_External_Non_Urgent_Payment_Model11_[WEB]</t>
-  </si>
-  <si>
-    <t>C70905</t>
-  </si>
-  <si>
-    <t>Payments_Domestic_Payments_External_Urgent_Payment_Model97_Invalid_Bez_Poziva_Na_Broj_[WEB]</t>
-  </si>
-  <si>
-    <t>C70906</t>
-  </si>
-  <si>
-    <t>Payments_Domestic_Payments_External_Non_Urgent_Payment_Model97_[WEB]</t>
-  </si>
-  <si>
-    <t>C70907</t>
-  </si>
-  <si>
-    <t>Payments_Domestic_Payments_Budzetski_Urgent_Payment_Purpose_Code_289_Invalid_[WEB]</t>
-  </si>
-  <si>
-    <t>C70908</t>
-  </si>
-  <si>
-    <t>Payments_Domestic_Payments_Budzetski_Urgent_Payment_Without_Reference_Number_Invalid_[WEB]</t>
-  </si>
-  <si>
-    <t>C70909</t>
-  </si>
-  <si>
-    <t>Payments_Domestic_Payments_Budzetski_Urgent_Payment_Model97_[WEB]</t>
-  </si>
-  <si>
-    <t>C70910</t>
-  </si>
-  <si>
-    <t>Payments_Domestic_Payments_Budzetski_Non_Urgent_Payment_Model97_[WEB]</t>
-  </si>
-  <si>
-    <t>C70911</t>
-  </si>
-  <si>
-    <t>Payments_Domestic_Payments_External_Urgent_Payment_Model97_[WEB]</t>
-  </si>
-  <si>
-    <t>C70912</t>
-  </si>
-  <si>
-    <t>Payments_Domestic_Payments_External_Urgent_Payment_Model11_[WEB]</t>
-  </si>
-  <si>
-    <t>C70913</t>
-  </si>
-  <si>
-    <t>Payments_Domestic_Payments_External_Non_Urgent_Payment_No_Model_[WEB]</t>
-  </si>
-  <si>
-    <t>C70914</t>
-  </si>
-  <si>
-    <t>Payments_Recipient_Last_5_Payments_Of_Recipient_[WEB]-View_And_Repeat</t>
-  </si>
-  <si>
-    <t>C70915</t>
-  </si>
-  <si>
-    <t>Payments_Own_Account_Transfer_From_Current_Foreign_Account_To_Current_Foreign_Account_[WEB]</t>
-  </si>
-  <si>
-    <t>C70916</t>
-  </si>
-  <si>
-    <t>Payments_Own_Account_Transfer_To_Loan_[WEB]</t>
-  </si>
-  <si>
-    <t>C70917</t>
-  </si>
-  <si>
-    <t>Payments_Payments_Archive_Payments_Details_[WEB]</t>
-  </si>
-  <si>
-    <t>C70918</t>
-  </si>
-  <si>
-    <t>Payments_Upcoming_Payments_Details_Of_Payments_Transaction_On_The_List_Of_Transaction_[WEB]</t>
-  </si>
-  <si>
-    <t>C70919</t>
-  </si>
-  <si>
-    <t>Payments_Currency_Exchange_[WEB]-Buy_From_Payment</t>
-  </si>
-  <si>
-    <t>C70920</t>
-  </si>
-  <si>
-    <t>Payments_Currency_Exchange_[WEB]-Sell_From_Payment</t>
-  </si>
-  <si>
-    <t>C70921</t>
-  </si>
-  <si>
-    <t>Saving_Accounts_Transactions_Download_Option_[WEB]</t>
-  </si>
-  <si>
-    <t>C70922</t>
-  </si>
-  <si>
-    <t>Savings_Accounts_Transactions_Filter_By_Date_Date_Picker_[WEB]</t>
-  </si>
-  <si>
-    <t>C70923</t>
-  </si>
-  <si>
-    <t>Payments_Recipient_Template_List_[WEB]</t>
-  </si>
-  <si>
-    <t>C70924</t>
-  </si>
-  <si>
-    <t>Credit_Cards_Details_Card_Details_[WEB]</t>
-  </si>
-  <si>
-    <t>C70925</t>
-  </si>
-  <si>
-    <t>Payments_Payments_Arhive_Resubmit_Payments_From_Past_Payment_List_[WEB]-Internal_Transfer</t>
-  </si>
-  <si>
     <t>C70926</t>
   </si>
   <si>
-    <t>Payments_Specific_Payment_Credit_Card_Repayment_[WEB]-From_Current_Domestic_Account</t>
+    <t>Credit_Cards_Details_Financial_Details_[WEB]</t>
   </si>
   <si>
     <t>C70927</t>
   </si>
   <si>
-    <t>Payments_Specific_Payment_Credit_Card_Repayment_[WEB]-From_Savings_Account</t>
+    <t>Credit_Cards_Transactions_List_[WEB]</t>
   </si>
   <si>
     <t>C70928</t>
   </si>
   <si>
-    <t>Payments_Payments_Arhive_Resubmit_Payments_From_Past_Payment_List_[WEB]-Domestic_Payment</t>
+    <t>Current_Foreign_Accounts_Transactions_Details_[WEB]</t>
   </si>
   <si>
     <t>C70929</t>
   </si>
   <si>
-    <t>Payments_Payments_Arhive_Resubmit_Payments_From_Past_Payment_List_[WEB]-Prenesi</t>
+    <t>Current_Accounts_RSD_Statemants_Downloads_[WEB]</t>
   </si>
   <si>
     <t>C70930</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts_Statemants_Downloads_[WEB]</t>
+  </si>
+  <si>
+    <t>C70931</t>
+  </si>
+  <si>
+    <t>Savings_Accounts_Transactions_Filter_By_Date_Predefined_Date_Range_[WEB]</t>
+  </si>
+  <si>
+    <t>C70932</t>
+  </si>
+  <si>
+    <t>Savings_Accounts_Transactions_Filter_By_Type_[WEB]</t>
+  </si>
+  <si>
+    <t>C70933</t>
+  </si>
+  <si>
+    <t>Savings_Accounts_Transactions_Filter_By_Amount_[WEB]</t>
+  </si>
+  <si>
+    <t>C70934</t>
+  </si>
+  <si>
+    <t>Savings_Accounts_Transactions_Filter_By_Date_Date_Picker_Invalid_[WEB]</t>
+  </si>
+  <si>
+    <t>C70935</t>
+  </si>
+  <si>
+    <t>Savings_Accounts_Transactions_Filter_Multiple_Filter_Invalid_[WEB]</t>
+  </si>
+  <si>
+    <t>C70936</t>
+  </si>
+  <si>
+    <t>Savings_Accounts_Transactions_Search_[WEB]</t>
+  </si>
+  <si>
+    <t>C70937</t>
+  </si>
+  <si>
+    <t>Credit_Cards_Transactions_Filter_By_Date_Predefined_Date_Range_[WEB]</t>
+  </si>
+  <si>
+    <t>C70938</t>
+  </si>
+  <si>
+    <t>C70939</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts_Header_Display_[WEB]</t>
+  </si>
+  <si>
+    <t>C70940</t>
+  </si>
+  <si>
+    <t>Credit_Cards_Transactions_Search_Option_[WEB]</t>
+  </si>
+  <si>
+    <t>C70941</t>
   </si>
 </sst>
 </file>
@@ -1675,17 +1768,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1739,18 +1835,6 @@
     <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2018,22 +2102,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F167"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="5"/>
+  <dimension ref="A1:F192"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="94.1428571428571" customWidth="1"/>
-    <col min="2" max="2" width="11.7142857142857" customWidth="1"/>
-    <col min="3" max="3" width="9" style="2"/>
+    <col min="1" max="1" width="91.1388888888889" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" customFormat="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
@@ -2050,10 +2132,10 @@
       <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
@@ -2063,37 +2145,37 @@
         <v>10</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" spans="1:6">
+      <c r="A3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
+      <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" spans="1:6">
       <c r="A4" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D4" s="1" t="s">
@@ -2103,17 +2185,17 @@
         <v>10</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" spans="1:6">
       <c r="A5" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D5" s="1" t="s">
@@ -2123,37 +2205,37 @@
         <v>10</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" spans="1:6">
       <c r="A6" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" spans="1:6">
       <c r="A7" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D7" s="1" t="s">
@@ -2163,17 +2245,17 @@
         <v>10</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" spans="1:6">
       <c r="A8" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D8" s="1" t="s">
@@ -2183,17 +2265,17 @@
         <v>10</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" spans="1:6">
       <c r="A9" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D9" s="1" t="s">
@@ -2203,17 +2285,17 @@
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" customFormat="1" spans="1:6">
       <c r="A10" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D10" s="1" t="s">
@@ -2223,37 +2305,37 @@
         <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" customFormat="1" spans="1:6">
       <c r="A11" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" customFormat="1" spans="1:6">
       <c r="A12" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="1" t="s">
@@ -2263,17 +2345,17 @@
         <v>10</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" customFormat="1" spans="1:6">
       <c r="A13" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
@@ -2283,17 +2365,17 @@
         <v>10</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" customFormat="1" spans="1:6">
       <c r="A14" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="1" t="s">
@@ -2303,17 +2385,17 @@
         <v>10</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" customFormat="1" spans="1:6">
       <c r="A15" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D15" s="1" t="s">
@@ -2323,17 +2405,17 @@
         <v>10</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" customFormat="1" spans="1:6">
       <c r="A16" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D16" s="1" t="s">
@@ -2343,17 +2425,17 @@
         <v>10</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" customFormat="1" spans="1:6">
       <c r="A17" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D17" s="1" t="s">
@@ -2363,17 +2445,17 @@
         <v>10</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" customFormat="1" spans="1:6">
       <c r="A18" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D18" s="1" t="s">
@@ -2383,37 +2465,37 @@
         <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" customFormat="1" spans="1:6">
       <c r="A19" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E19" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F19" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" customFormat="1" spans="1:6">
       <c r="A20" t="s">
         <v>46</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D20" s="1" t="s">
@@ -2423,37 +2505,37 @@
         <v>10</v>
       </c>
       <c r="F20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" customFormat="1" spans="1:6">
       <c r="A21" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E21" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F21" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" customFormat="1" spans="1:6">
       <c r="A22" t="s">
         <v>50</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D22" s="1" t="s">
@@ -2463,17 +2545,17 @@
         <v>10</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" customFormat="1" spans="1:6">
       <c r="A23" t="s">
         <v>52</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D23" s="1" t="s">
@@ -2483,37 +2565,37 @@
         <v>10</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" customFormat="1" spans="1:6">
       <c r="A24" t="s">
         <v>54</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E24" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" customFormat="1" spans="1:6">
       <c r="A25" t="s">
         <v>56</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D25" s="1" t="s">
@@ -2523,17 +2605,17 @@
         <v>10</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" customFormat="1" spans="1:6">
       <c r="A26" t="s">
         <v>58</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D26" s="1" t="s">
@@ -2543,17 +2625,17 @@
         <v>10</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" customFormat="1" spans="1:6">
       <c r="A27" t="s">
         <v>60</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D27" s="1" t="s">
@@ -2563,77 +2645,77 @@
         <v>10</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" customFormat="1" spans="1:6">
       <c r="A28" t="s">
         <v>62</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E28" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" customFormat="1" spans="1:6">
       <c r="A29" t="s">
         <v>64</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E29" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" customFormat="1" spans="1:6">
       <c r="A30" t="s">
         <v>66</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E30" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" customFormat="1" spans="1:6">
       <c r="A31" t="s">
         <v>68</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D31" s="1" t="s">
@@ -2643,17 +2725,17 @@
         <v>10</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" customFormat="1" spans="1:6">
       <c r="A32" t="s">
         <v>70</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D32" s="1" t="s">
@@ -2663,17 +2745,17 @@
         <v>10</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" customFormat="1" spans="1:6">
       <c r="A33" t="s">
         <v>72</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D33" s="1" t="s">
@@ -2683,17 +2765,17 @@
         <v>10</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" customFormat="1" spans="1:6">
       <c r="A34" t="s">
         <v>74</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D34" s="1" t="s">
@@ -2703,57 +2785,57 @@
         <v>10</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" customFormat="1" spans="1:6">
       <c r="A35" t="s">
         <v>76</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E35" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" customFormat="1" spans="1:6">
       <c r="A36" t="s">
         <v>78</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E36" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" customFormat="1" spans="1:6">
       <c r="A37" t="s">
         <v>80</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C37" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D37" s="1" t="s">
@@ -2763,17 +2845,17 @@
         <v>10</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" customFormat="1" spans="1:6">
       <c r="A38" t="s">
         <v>82</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D38" s="1" t="s">
@@ -2783,57 +2865,57 @@
         <v>10</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" customFormat="1" spans="1:6">
       <c r="A39" t="s">
         <v>84</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E39" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" customFormat="1" spans="1:6">
       <c r="A40" t="s">
         <v>86</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E40" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" customFormat="1" spans="1:6">
       <c r="A41" t="s">
         <v>88</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C41" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D41" s="1" t="s">
@@ -2843,57 +2925,57 @@
         <v>10</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" customFormat="1" spans="1:6">
       <c r="A42" t="s">
         <v>90</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C42" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E42" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F42" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" customFormat="1" spans="1:6">
       <c r="A43" t="s">
         <v>92</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C43" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E43" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F43" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" customFormat="1" spans="1:6">
       <c r="A44" t="s">
         <v>94</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B44" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C44" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D44" s="1" t="s">
@@ -2903,17 +2985,17 @@
         <v>10</v>
       </c>
       <c r="F44" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" customFormat="1" spans="1:6">
       <c r="A45" t="s">
         <v>96</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="C45" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D45" s="1" t="s">
@@ -2923,17 +3005,17 @@
         <v>10</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" customFormat="1" spans="1:6">
       <c r="A46" t="s">
         <v>98</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D46" s="1" t="s">
@@ -2943,17 +3025,17 @@
         <v>10</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" customFormat="1" spans="1:6">
       <c r="A47" t="s">
         <v>100</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="C47" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D47" s="1" t="s">
@@ -2963,37 +3045,37 @@
         <v>10</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48" customFormat="1" spans="1:6">
       <c r="A48" t="s">
         <v>102</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C48" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E48" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" customFormat="1" spans="1:6">
       <c r="A49" t="s">
         <v>104</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B49" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C49" s="4" t="s">
+      <c r="C49" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D49" s="1" t="s">
@@ -3003,37 +3085,37 @@
         <v>10</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" customFormat="1" spans="1:6">
       <c r="A50" t="s">
         <v>106</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B50" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C50" s="4" t="s">
+      <c r="C50" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E50" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" customFormat="1" spans="1:6">
       <c r="A51" t="s">
         <v>108</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="B51" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C51" s="4" t="s">
+      <c r="C51" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D51" s="1" t="s">
@@ -3043,17 +3125,17 @@
         <v>10</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" customFormat="1" spans="1:6">
       <c r="A52" t="s">
         <v>110</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B52" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="C52" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D52" s="1" t="s">
@@ -3063,97 +3145,97 @@
         <v>10</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" customFormat="1" spans="1:6">
       <c r="A53" t="s">
         <v>112</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="B53" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C53" s="4" t="s">
+      <c r="C53" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E53" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" customFormat="1" spans="1:6">
       <c r="A54" t="s">
         <v>114</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="B54" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="C54" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E54" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" customFormat="1" spans="1:6">
       <c r="A55" t="s">
         <v>116</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="B55" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C55" s="4" t="s">
+      <c r="C55" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E55" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56" customFormat="1" spans="1:6">
       <c r="A56" t="s">
         <v>118</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="B56" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C56" s="4" t="s">
+      <c r="C56" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E56" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" customFormat="1" spans="1:6">
       <c r="A57" t="s">
         <v>120</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="B57" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C57" s="4" t="s">
+      <c r="C57" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D57" s="1" t="s">
@@ -3163,57 +3245,57 @@
         <v>10</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" customFormat="1" spans="1:6">
       <c r="A58" t="s">
         <v>122</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="B58" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C58" s="4" t="s">
+      <c r="C58" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E58" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" customFormat="1" spans="1:6">
       <c r="A59" t="s">
         <v>124</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="B59" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C59" s="4" t="s">
+      <c r="C59" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E59" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" customFormat="1" spans="1:6">
       <c r="A60" t="s">
         <v>126</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B60" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C60" s="4" t="s">
+      <c r="C60" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D60" s="1" t="s">
@@ -3223,17 +3305,17 @@
         <v>10</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" customFormat="1" spans="1:6">
       <c r="A61" t="s">
         <v>128</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="B61" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C61" s="4" t="s">
+      <c r="C61" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D61" s="1" t="s">
@@ -3243,17 +3325,17 @@
         <v>10</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62" customFormat="1" spans="1:6">
       <c r="A62" t="s">
         <v>130</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="B62" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C62" s="4" t="s">
+      <c r="C62" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D62" s="1" t="s">
@@ -3263,37 +3345,37 @@
         <v>10</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" customFormat="1" spans="1:6">
       <c r="A63" t="s">
         <v>132</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="B63" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C63" s="4" t="s">
+      <c r="C63" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E63" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64" customFormat="1" spans="1:6">
       <c r="A64" t="s">
         <v>134</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="B64" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="C64" s="4" t="s">
+      <c r="C64" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D64" s="1" t="s">
@@ -3303,17 +3385,17 @@
         <v>10</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65" customFormat="1" spans="1:6">
       <c r="A65" t="s">
         <v>136</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="B65" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C65" s="4" t="s">
+      <c r="C65" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D65" s="1" t="s">
@@ -3323,17 +3405,17 @@
         <v>10</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="66" customFormat="1" spans="1:6">
       <c r="A66" t="s">
         <v>138</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="B66" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C66" s="4" t="s">
+      <c r="C66" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D66" s="1" t="s">
@@ -3343,57 +3425,57 @@
         <v>10</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" customFormat="1" spans="1:6">
       <c r="A67" t="s">
         <v>140</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="B67" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="C67" s="4" t="s">
+      <c r="C67" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E67" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="68" customFormat="1" spans="1:6">
       <c r="A68" t="s">
         <v>142</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="B68" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C68" s="4" t="s">
+      <c r="C68" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E68" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69" customFormat="1" spans="1:6">
       <c r="A69" t="s">
         <v>144</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="B69" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C69" s="4" t="s">
+      <c r="C69" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D69" s="1" t="s">
@@ -3403,17 +3485,17 @@
         <v>10</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="70" customFormat="1" spans="1:6">
       <c r="A70" t="s">
         <v>146</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="B70" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="C70" s="4" t="s">
+      <c r="C70" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D70" s="1" t="s">
@@ -3423,17 +3505,17 @@
         <v>10</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="71" customFormat="1" spans="1:6">
       <c r="A71" t="s">
         <v>148</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="B71" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C71" s="4" t="s">
+      <c r="C71" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D71" s="1" t="s">
@@ -3443,17 +3525,17 @@
         <v>10</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72" customFormat="1" spans="1:6">
       <c r="A72" t="s">
         <v>150</v>
       </c>
-      <c r="B72" s="3" t="s">
+      <c r="B72" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="C72" s="4" t="s">
+      <c r="C72" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D72" s="1" t="s">
@@ -3463,17 +3545,17 @@
         <v>10</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" customFormat="1" spans="1:6">
       <c r="A73" t="s">
         <v>152</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="B73" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C73" s="4" t="s">
+      <c r="C73" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D73" s="1" t="s">
@@ -3483,37 +3565,37 @@
         <v>10</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="74" customFormat="1" spans="1:6">
       <c r="A74" t="s">
         <v>154</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="B74" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C74" s="4" t="s">
+      <c r="C74" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E74" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="75" customFormat="1" spans="1:6">
       <c r="A75" t="s">
         <v>156</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="B75" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="C75" s="4" t="s">
+      <c r="C75" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D75" s="1" t="s">
@@ -3523,137 +3605,137 @@
         <v>10</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="76" customFormat="1" spans="1:6">
       <c r="A76" t="s">
         <v>158</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="B76" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="C76" s="4" t="s">
+      <c r="C76" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E76" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77" customFormat="1" spans="1:6">
       <c r="A77" t="s">
         <v>160</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="B77" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="C77" s="4" t="s">
+      <c r="C77" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E77" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="78" customFormat="1" spans="1:6">
       <c r="A78" t="s">
         <v>162</v>
       </c>
-      <c r="B78" s="3" t="s">
+      <c r="B78" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="C78" s="4" t="s">
+      <c r="C78" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E78" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="79" customFormat="1" spans="1:6">
       <c r="A79" t="s">
         <v>164</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="B79" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C79" s="4" t="s">
+      <c r="C79" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E79" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="80" customFormat="1" spans="1:6">
       <c r="A80" t="s">
         <v>166</v>
       </c>
-      <c r="B80" s="3" t="s">
+      <c r="B80" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="C80" s="4" t="s">
+      <c r="C80" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E80" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="81" customFormat="1" spans="1:6">
       <c r="A81" t="s">
         <v>168</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="B81" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C81" s="4" t="s">
+      <c r="C81" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E81" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="82" customFormat="1" spans="1:6">
       <c r="A82" t="s">
         <v>170</v>
       </c>
-      <c r="B82" s="3" t="s">
+      <c r="B82" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="C82" s="4" t="s">
+      <c r="C82" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D82" s="1" t="s">
@@ -3663,17 +3745,17 @@
         <v>10</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="83" customFormat="1" spans="1:6">
       <c r="A83" t="s">
         <v>172</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="B83" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C83" s="4" t="s">
+      <c r="C83" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D83" s="1" t="s">
@@ -3683,37 +3765,37 @@
         <v>10</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" customFormat="1" spans="1:6">
       <c r="A84" t="s">
         <v>174</v>
       </c>
-      <c r="B84" s="3" t="s">
+      <c r="B84" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C84" s="4" t="s">
+      <c r="C84" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E84" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="85" customFormat="1" spans="1:6">
       <c r="A85" t="s">
         <v>176</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="B85" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C85" s="4" t="s">
+      <c r="C85" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D85" s="1" t="s">
@@ -3723,17 +3805,17 @@
         <v>10</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="86" customFormat="1" spans="1:6">
       <c r="A86" t="s">
         <v>178</v>
       </c>
-      <c r="B86" s="3" t="s">
+      <c r="B86" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C86" s="4" t="s">
+      <c r="C86" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D86" s="1" t="s">
@@ -3743,17 +3825,17 @@
         <v>10</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="87" customFormat="1" spans="1:6">
       <c r="A87" t="s">
         <v>166</v>
       </c>
-      <c r="B87" s="3" t="s">
+      <c r="B87" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C87" s="4" t="s">
+      <c r="C87" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D87" s="1" t="s">
@@ -3763,37 +3845,37 @@
         <v>10</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="88" customFormat="1" spans="1:6">
       <c r="A88" t="s">
         <v>181</v>
       </c>
-      <c r="B88" s="3" t="s">
+      <c r="B88" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C88" s="4" t="s">
+      <c r="C88" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E88" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="89" customFormat="1" spans="1:6">
       <c r="A89" t="s">
         <v>183</v>
       </c>
-      <c r="B89" s="3" t="s">
+      <c r="B89" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C89" s="4" t="s">
+      <c r="C89" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D89" s="1" t="s">
@@ -3803,17 +3885,17 @@
         <v>10</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90" customFormat="1" spans="1:6">
       <c r="A90" t="s">
         <v>185</v>
       </c>
-      <c r="B90" s="3" t="s">
+      <c r="B90" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C90" s="4" t="s">
+      <c r="C90" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D90" s="1" t="s">
@@ -3823,57 +3905,57 @@
         <v>10</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="91" customFormat="1" spans="1:6">
       <c r="A91" t="s">
         <v>187</v>
       </c>
-      <c r="B91" s="3" t="s">
+      <c r="B91" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="C91" s="4" t="s">
+      <c r="C91" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E91" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92" customFormat="1" spans="1:6">
       <c r="A92" t="s">
         <v>189</v>
       </c>
-      <c r="B92" s="3" t="s">
+      <c r="B92" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="C92" s="4" t="s">
+      <c r="C92" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E92" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="93" customFormat="1" spans="1:6">
       <c r="A93" t="s">
         <v>191</v>
       </c>
-      <c r="B93" s="3" t="s">
+      <c r="B93" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="C93" s="4" t="s">
+      <c r="C93" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D93" s="1" t="s">
@@ -3883,17 +3965,17 @@
         <v>10</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="94" customFormat="1" spans="1:6">
       <c r="A94" t="s">
         <v>193</v>
       </c>
-      <c r="B94" s="3" t="s">
+      <c r="B94" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="C94" s="4" t="s">
+      <c r="C94" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D94" s="1" t="s">
@@ -3903,17 +3985,17 @@
         <v>10</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95" customFormat="1" spans="1:6">
       <c r="A95" t="s">
         <v>195</v>
       </c>
-      <c r="B95" s="3" t="s">
+      <c r="B95" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C95" s="4" t="s">
+      <c r="C95" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D95" s="1" t="s">
@@ -3923,17 +4005,17 @@
         <v>10</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="96" customFormat="1" spans="1:6">
       <c r="A96" t="s">
         <v>197</v>
       </c>
-      <c r="B96" s="3" t="s">
+      <c r="B96" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="C96" s="4" t="s">
+      <c r="C96" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D96" s="1" t="s">
@@ -3943,17 +4025,17 @@
         <v>10</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="97" customFormat="1" spans="1:6">
       <c r="A97" t="s">
         <v>199</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="B97" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="C97" s="4" t="s">
+      <c r="C97" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D97" s="1" t="s">
@@ -3963,17 +4045,17 @@
         <v>10</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="98" customFormat="1" spans="1:6">
       <c r="A98" t="s">
         <v>201</v>
       </c>
-      <c r="B98" s="3" t="s">
+      <c r="B98" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="C98" s="4" t="s">
+      <c r="C98" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D98" s="1" t="s">
@@ -3983,17 +4065,17 @@
         <v>10</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="99" customFormat="1" spans="1:6">
       <c r="A99" t="s">
         <v>203</v>
       </c>
-      <c r="B99" s="3" t="s">
+      <c r="B99" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="C99" s="4" t="s">
+      <c r="C99" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D99" s="1" t="s">
@@ -4003,17 +4085,17 @@
         <v>10</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="100" customFormat="1" spans="1:6">
       <c r="A100" t="s">
         <v>205</v>
       </c>
-      <c r="B100" s="3" t="s">
+      <c r="B100" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C100" s="4" t="s">
+      <c r="C100" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D100" s="1" t="s">
@@ -4023,37 +4105,37 @@
         <v>10</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" customFormat="1" spans="1:6">
       <c r="A101" t="s">
         <v>207</v>
       </c>
-      <c r="B101" s="3" t="s">
+      <c r="B101" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="C101" s="4" t="s">
+      <c r="C101" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E101" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="102" customFormat="1" spans="1:6">
       <c r="A102" t="s">
         <v>209</v>
       </c>
-      <c r="B102" s="3" t="s">
+      <c r="B102" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C102" s="4" t="s">
+      <c r="C102" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D102" s="1" t="s">
@@ -4063,17 +4145,17 @@
         <v>10</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="103" customFormat="1" spans="1:6">
       <c r="A103" t="s">
         <v>211</v>
       </c>
-      <c r="B103" s="3" t="s">
+      <c r="B103" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C103" s="4" t="s">
+      <c r="C103" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D103" s="1" t="s">
@@ -4083,17 +4165,17 @@
         <v>10</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="104" customFormat="1" spans="1:6">
       <c r="A104" t="s">
         <v>213</v>
       </c>
-      <c r="B104" s="3" t="s">
+      <c r="B104" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="C104" s="4" t="s">
+      <c r="C104" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D104" s="1" t="s">
@@ -4103,97 +4185,97 @@
         <v>10</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="105" customFormat="1" spans="1:6">
       <c r="A105" t="s">
         <v>215</v>
       </c>
-      <c r="B105" s="3" t="s">
+      <c r="B105" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="C105" s="4" t="s">
+      <c r="C105" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E105" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="106" customFormat="1" spans="1:6">
       <c r="A106" t="s">
         <v>217</v>
       </c>
-      <c r="B106" s="3" t="s">
+      <c r="B106" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="C106" s="4" t="s">
+      <c r="C106" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E106" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="107" customFormat="1" spans="1:6">
       <c r="A107" t="s">
         <v>219</v>
       </c>
-      <c r="B107" s="3" t="s">
+      <c r="B107" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="C107" s="4" t="s">
+      <c r="C107" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E107" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="108" customFormat="1" spans="1:6">
       <c r="A108" t="s">
         <v>221</v>
       </c>
-      <c r="B108" s="3" t="s">
+      <c r="B108" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="C108" s="4" t="s">
+      <c r="C108" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E108" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="109" customFormat="1" spans="1:6">
       <c r="A109" t="s">
         <v>223</v>
       </c>
-      <c r="B109" s="3" t="s">
+      <c r="B109" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="C109" s="4" t="s">
+      <c r="C109" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D109" s="1" t="s">
@@ -4203,17 +4285,17 @@
         <v>10</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="110" customFormat="1" spans="1:6">
       <c r="A110" t="s">
         <v>225</v>
       </c>
-      <c r="B110" s="3" t="s">
+      <c r="B110" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="C110" s="4" t="s">
+      <c r="C110" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D110" s="1" t="s">
@@ -4223,37 +4305,37 @@
         <v>10</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="111" customFormat="1" spans="1:6">
       <c r="A111" t="s">
         <v>227</v>
       </c>
-      <c r="B111" s="3" t="s">
+      <c r="B111" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="C111" s="4" t="s">
+      <c r="C111" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D111" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E111" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="112" customFormat="1" spans="1:6">
       <c r="A112" t="s">
         <v>229</v>
       </c>
-      <c r="B112" s="3" t="s">
+      <c r="B112" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="C112" s="4" t="s">
+      <c r="C112" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D112" s="1" t="s">
@@ -4263,37 +4345,37 @@
         <v>10</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="113" customFormat="1" spans="1:6">
       <c r="A113" t="s">
         <v>231</v>
       </c>
-      <c r="B113" s="3" t="s">
+      <c r="B113" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="C113" s="4" t="s">
+      <c r="C113" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E113" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="114" customFormat="1" spans="1:6">
       <c r="A114" t="s">
         <v>233</v>
       </c>
-      <c r="B114" s="3" t="s">
+      <c r="B114" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="C114" s="4" t="s">
+      <c r="C114" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D114" s="1" t="s">
@@ -4303,77 +4385,77 @@
         <v>10</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="115" customFormat="1" spans="1:6">
       <c r="A115" t="s">
         <v>235</v>
       </c>
-      <c r="B115" s="3" t="s">
+      <c r="B115" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="C115" s="4" t="s">
+      <c r="C115" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E115" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="116" customFormat="1" spans="1:6">
       <c r="A116" t="s">
         <v>237</v>
       </c>
-      <c r="B116" s="3" t="s">
+      <c r="B116" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="C116" s="4" t="s">
+      <c r="C116" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E116" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="117" customFormat="1" spans="1:6">
       <c r="A117" t="s">
         <v>239</v>
       </c>
-      <c r="B117" s="3" t="s">
+      <c r="B117" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="C117" s="4" t="s">
+      <c r="C117" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E117" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="118" customFormat="1" spans="1:6">
       <c r="A118" t="s">
         <v>241</v>
       </c>
-      <c r="B118" s="3" t="s">
+      <c r="B118" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="C118" s="4" t="s">
+      <c r="C118" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D118" s="1" t="s">
@@ -4383,37 +4465,37 @@
         <v>10</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="119" customFormat="1" spans="1:6">
       <c r="A119" t="s">
         <v>243</v>
       </c>
-      <c r="B119" s="3" t="s">
+      <c r="B119" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="C119" s="4" t="s">
+      <c r="C119" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E119" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="120" customFormat="1" spans="1:6">
       <c r="A120" t="s">
         <v>245</v>
       </c>
-      <c r="B120" s="3" t="s">
+      <c r="B120" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="C120" s="4" t="s">
+      <c r="C120" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D120" s="1" t="s">
@@ -4423,17 +4505,17 @@
         <v>10</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="121" customFormat="1" spans="1:6">
       <c r="A121" t="s">
         <v>247</v>
       </c>
-      <c r="B121" s="3" t="s">
+      <c r="B121" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="C121" s="4" t="s">
+      <c r="C121" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D121" s="1" t="s">
@@ -4443,17 +4525,17 @@
         <v>10</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="122" customFormat="1" spans="1:6">
       <c r="A122" t="s">
         <v>249</v>
       </c>
-      <c r="B122" s="3" t="s">
+      <c r="B122" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="C122" s="4" t="s">
+      <c r="C122" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D122" s="1" t="s">
@@ -4463,77 +4545,77 @@
         <v>10</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="123" customFormat="1" spans="1:6">
       <c r="A123" t="s">
         <v>251</v>
       </c>
-      <c r="B123" s="3" t="s">
+      <c r="B123" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="C123" s="4" t="s">
+      <c r="C123" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E123" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="124" customFormat="1" spans="1:6">
       <c r="A124" t="s">
         <v>253</v>
       </c>
-      <c r="B124" s="3" t="s">
+      <c r="B124" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="C124" s="4" t="s">
+      <c r="C124" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D124" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E124" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="125" customFormat="1" spans="1:6">
       <c r="A125" t="s">
         <v>255</v>
       </c>
-      <c r="B125" s="3" t="s">
+      <c r="B125" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="C125" s="4" t="s">
+      <c r="C125" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D125" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E125" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="126" customFormat="1" spans="1:6">
       <c r="A126" t="s">
         <v>257</v>
       </c>
-      <c r="B126" s="3" t="s">
+      <c r="B126" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="C126" s="4" t="s">
+      <c r="C126" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D126" s="1" t="s">
@@ -4543,17 +4625,17 @@
         <v>10</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="127" customFormat="1" spans="1:6">
       <c r="A127" t="s">
         <v>259</v>
       </c>
-      <c r="B127" s="3" t="s">
+      <c r="B127" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="C127" s="4" t="s">
+      <c r="C127" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D127" s="1" t="s">
@@ -4563,17 +4645,17 @@
         <v>10</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="128" customFormat="1" spans="1:6">
       <c r="A128" t="s">
         <v>261</v>
       </c>
-      <c r="B128" s="3" t="s">
+      <c r="B128" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="C128" s="4" t="s">
+      <c r="C128" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D128" s="1" t="s">
@@ -4583,796 +4665,1290 @@
         <v>10</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="129" customFormat="1" spans="1:6">
       <c r="A129" t="s">
         <v>263</v>
       </c>
-      <c r="B129" s="3" t="s">
+      <c r="B129" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="C129" s="4" t="s">
+      <c r="C129" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D129" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E129" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="130" customFormat="1" spans="1:6">
       <c r="A130" t="s">
         <v>265</v>
       </c>
-      <c r="B130" s="3" t="s">
+      <c r="B130" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="C130" s="4" t="s">
+      <c r="C130" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E130" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="131" customFormat="1" spans="1:6">
       <c r="A131" t="s">
         <v>267</v>
       </c>
-      <c r="B131" s="3" t="s">
+      <c r="B131" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="C131" s="4" t="s">
+      <c r="C131" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D131" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E131" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="132" customFormat="1" spans="1:6">
       <c r="A132" t="s">
         <v>269</v>
       </c>
-      <c r="B132" s="3" t="s">
+      <c r="B132" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="C132" s="4" t="s">
+      <c r="C132" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E132" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="133" customFormat="1" spans="1:6">
       <c r="A133" t="s">
         <v>271</v>
       </c>
-      <c r="B133" s="3" t="s">
+      <c r="B133" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="C133" s="4" t="s">
+      <c r="C133" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E133" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="134" customFormat="1" spans="1:6">
       <c r="A134" t="s">
         <v>273</v>
       </c>
-      <c r="B134" s="3" t="s">
+      <c r="B134" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="C134" s="4" t="s">
+      <c r="C134" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E134" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="135" customFormat="1" spans="1:6">
       <c r="A135" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="B135" s="3" t="s">
+      <c r="B135" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="C135" s="4" t="s">
+      <c r="C135" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D135" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E135" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="136" customFormat="1" spans="1:6">
       <c r="A136" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="B136" s="3" t="s">
+      <c r="B136" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="C136" s="4" t="s">
+      <c r="C136" s="1" t="s">
         <v>279</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E136" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="137" customFormat="1" spans="1:6">
       <c r="A137" t="s">
         <v>280</v>
       </c>
-      <c r="B137" s="3" t="s">
+      <c r="B137" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="C137" s="4" t="s">
+      <c r="C137" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D137" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E137" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="138" customFormat="1" spans="1:6">
       <c r="A138" t="s">
         <v>282</v>
       </c>
-      <c r="B138" s="3" t="s">
+      <c r="B138" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="C138" s="4" t="s">
+      <c r="C138" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D138" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E138" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="139" customFormat="1" spans="1:6">
       <c r="A139" t="s">
         <v>284</v>
       </c>
-      <c r="B139" s="3" t="s">
+      <c r="B139" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="C139" s="4" t="s">
+      <c r="C139" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D139" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E139" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="140" customFormat="1" spans="1:6">
       <c r="A140" t="s">
         <v>286</v>
       </c>
-      <c r="B140" s="3" t="s">
+      <c r="B140" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="C140" s="4" t="s">
+      <c r="C140" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D140" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E140" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="141" customFormat="1" spans="1:6">
       <c r="A141" t="s">
         <v>288</v>
       </c>
-      <c r="B141" s="3" t="s">
+      <c r="B141" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="C141" s="4" t="s">
+      <c r="C141" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D141" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E141" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="142" customFormat="1" spans="1:6">
       <c r="A142" t="s">
         <v>290</v>
       </c>
-      <c r="B142" s="3" t="s">
+      <c r="B142" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="C142" s="4" t="s">
+      <c r="C142" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D142" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E142" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="143" customFormat="1" spans="1:6">
       <c r="A143" t="s">
         <v>292</v>
       </c>
-      <c r="B143" s="3" t="s">
+      <c r="B143" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="C143" s="4" t="s">
+      <c r="C143" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D143" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E143" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="144" customFormat="1" spans="1:6">
       <c r="A144" t="s">
         <v>294</v>
       </c>
-      <c r="B144" s="3" t="s">
+      <c r="B144" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="C144" s="4" t="s">
+      <c r="C144" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D144" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E144" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="145" customFormat="1" spans="1:6">
       <c r="A145" t="s">
         <v>296</v>
       </c>
-      <c r="B145" s="3" t="s">
+      <c r="B145" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="C145" s="4" t="s">
+      <c r="C145" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D145" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E145" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="146" customFormat="1" spans="1:6">
       <c r="A146" t="s">
         <v>298</v>
       </c>
-      <c r="B146" s="3" t="s">
+      <c r="B146" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="C146" s="4" t="s">
+      <c r="C146" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D146" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E146" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="147" customFormat="1" spans="1:6">
       <c r="A147" t="s">
+        <v>280</v>
+      </c>
+      <c r="B147" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="B147" s="3" t="s">
+      <c r="C147" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E147" t="s">
+        <v>13</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="148" customFormat="1" spans="1:6">
+      <c r="A148" t="s">
         <v>301</v>
       </c>
-      <c r="C147" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E147" t="s">
-        <v>10</v>
-      </c>
-      <c r="F147" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6">
-      <c r="A148" t="s">
+      <c r="B148" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="B148" s="3" t="s">
+      <c r="C148" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E148" t="s">
+        <v>13</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="149" customFormat="1" spans="1:6">
+      <c r="A149" t="s">
         <v>303</v>
       </c>
-      <c r="C148" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E148" t="s">
-        <v>10</v>
-      </c>
-      <c r="F148" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6">
-      <c r="A149" t="s">
+      <c r="B149" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="B149" s="3" t="s">
+      <c r="C149" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E149" t="s">
+        <v>13</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="150" customFormat="1" spans="1:6">
+      <c r="A150" t="s">
         <v>305</v>
       </c>
-      <c r="C149" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E149" t="s">
-        <v>10</v>
-      </c>
-      <c r="F149" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6">
-      <c r="A150" t="s">
+      <c r="B150" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="B150" s="3" t="s">
+      <c r="C150" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E150" t="s">
+        <v>13</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="151" customFormat="1" spans="1:6">
+      <c r="A151" t="s">
         <v>307</v>
       </c>
-      <c r="C150" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E150" t="s">
-        <v>10</v>
-      </c>
-      <c r="F150" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6">
-      <c r="A151" t="s">
+      <c r="B151" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="B151" s="3" t="s">
+      <c r="C151" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E151" t="s">
+        <v>13</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="152" customFormat="1" spans="1:6">
+      <c r="A152" t="s">
         <v>309</v>
       </c>
-      <c r="C151" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E151" t="s">
-        <v>10</v>
-      </c>
-      <c r="F151" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6">
-      <c r="A152" t="s">
+      <c r="B152" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E152" t="s">
+        <v>13</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="153" customFormat="1" spans="1:6">
+      <c r="A153" t="s">
         <v>310</v>
       </c>
-      <c r="B152" s="3" t="s">
+      <c r="B153" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C153" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E153" t="s">
+        <v>13</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="154" customFormat="1" spans="1:6">
+      <c r="A154" t="s">
         <v>311</v>
       </c>
-      <c r="C152" s="4">
-        <v>3</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E152" t="s">
-        <v>10</v>
-      </c>
-      <c r="F152" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6">
-      <c r="A153" t="s">
+      <c r="B154" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E154" t="s">
+        <v>13</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="155" customFormat="1" spans="1:6">
+      <c r="A155" t="s">
         <v>312</v>
       </c>
-      <c r="B153" s="3" t="s">
+      <c r="B155" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C155" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E155" t="s">
+        <v>13</v>
+      </c>
+      <c r="F155" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="156" customFormat="1" spans="1:6">
+      <c r="A156" t="s">
         <v>313</v>
       </c>
-      <c r="C153" s="4">
-        <v>3</v>
-      </c>
-      <c r="D153" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E153" t="s">
-        <v>10</v>
-      </c>
-      <c r="F153" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6">
-      <c r="A154" t="s">
+      <c r="B156" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E156" t="s">
+        <v>13</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="157" customFormat="1" spans="1:6">
+      <c r="A157" t="s">
         <v>314</v>
       </c>
-      <c r="B154" s="3" t="s">
+      <c r="B157" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C157" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E157" t="s">
+        <v>13</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="158" customFormat="1" spans="1:6">
+      <c r="A158" t="s">
         <v>315</v>
       </c>
-      <c r="C154" s="4">
-        <v>3</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E154" t="s">
-        <v>10</v>
-      </c>
-      <c r="F154" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6">
-      <c r="A155" t="s">
+      <c r="B158" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E158" t="s">
+        <v>13</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="159" customFormat="1" spans="1:6">
+      <c r="A159" t="s">
         <v>316</v>
       </c>
-      <c r="B155" s="3" t="s">
+      <c r="B159" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="C159" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E159" t="s">
+        <v>13</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="160" customFormat="1" spans="1:6">
+      <c r="A160" t="s">
         <v>317</v>
       </c>
-      <c r="C155" s="4">
-        <v>3</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E155" t="s">
-        <v>10</v>
-      </c>
-      <c r="F155" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6">
-      <c r="A156" t="s">
+      <c r="B160" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C160" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E160" t="s">
+        <v>13</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="161" customFormat="1" spans="1:6">
+      <c r="A161" t="s">
         <v>318</v>
       </c>
-      <c r="B156" s="3" t="s">
+      <c r="B161" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E161" t="s">
+        <v>13</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="162" customFormat="1" spans="1:6">
+      <c r="A162" t="s">
         <v>319</v>
       </c>
-      <c r="C156" s="4">
-        <v>3</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E156" t="s">
-        <v>10</v>
-      </c>
-      <c r="F156" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6">
-      <c r="A157" t="s">
+      <c r="B162" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E162" t="s">
+        <v>13</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="163" customFormat="1" spans="1:6">
+      <c r="A163" t="s">
         <v>320</v>
       </c>
-      <c r="B157" s="3" t="s">
+      <c r="B163" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C163" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E163" t="s">
+        <v>13</v>
+      </c>
+      <c r="F163" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="164" customFormat="1" spans="1:6">
+      <c r="A164" t="s">
         <v>321</v>
       </c>
-      <c r="C157" s="4">
-        <v>3</v>
-      </c>
-      <c r="D157" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E157" t="s">
-        <v>10</v>
-      </c>
-      <c r="F157" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6">
-      <c r="A158" t="s">
+      <c r="B164" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C164" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E164" t="s">
+        <v>13</v>
+      </c>
+      <c r="F164" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="165" customFormat="1" spans="1:6">
+      <c r="A165" t="s">
         <v>322</v>
       </c>
-      <c r="B158" s="3" t="s">
+      <c r="B165" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C165" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E165" t="s">
+        <v>13</v>
+      </c>
+      <c r="F165" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="166" customFormat="1" spans="1:6">
+      <c r="A166" t="s">
         <v>323</v>
       </c>
-      <c r="C158" s="4">
-        <v>3</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E158" t="s">
-        <v>10</v>
-      </c>
-      <c r="F158" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6">
-      <c r="A159" t="s">
+      <c r="B166" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="B159" s="3" t="s">
+      <c r="C166" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E166" t="s">
+        <v>13</v>
+      </c>
+      <c r="F166" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="167" customFormat="1" spans="1:6">
+      <c r="A167" t="s">
         <v>325</v>
       </c>
-      <c r="C159" s="4">
-        <v>3</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E159" t="s">
-        <v>10</v>
-      </c>
-      <c r="F159" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6">
-      <c r="A160" t="s">
+      <c r="B167" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="B160" s="3" t="s">
+      <c r="C167" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E167" t="s">
+        <v>13</v>
+      </c>
+      <c r="F167" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="168" customFormat="1" spans="1:6">
+      <c r="A168" t="s">
         <v>327</v>
       </c>
-      <c r="C160" s="4">
-        <v>3</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E160" t="s">
-        <v>10</v>
-      </c>
-      <c r="F160" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6">
-      <c r="A161" t="s">
+      <c r="B168" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="B161" s="3" t="s">
+      <c r="C168" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D168" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E168" t="s">
+        <v>13</v>
+      </c>
+      <c r="F168" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="169" customFormat="1" spans="1:6">
+      <c r="A169" t="s">
         <v>329</v>
       </c>
-      <c r="C161" s="4">
-        <v>3</v>
-      </c>
-      <c r="D161" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E161" t="s">
-        <v>10</v>
-      </c>
-      <c r="F161" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6">
-      <c r="A162" t="s">
+      <c r="B169" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="B162" s="3" t="s">
+      <c r="C169" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E169" t="s">
+        <v>13</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="170" customFormat="1" ht="15" customHeight="1" spans="1:6">
+      <c r="A170" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="C162" s="4">
-        <v>3</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E162" t="s">
-        <v>10</v>
-      </c>
-      <c r="F162" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6">
-      <c r="A163" t="s">
+      <c r="B170" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="B163" s="3" t="s">
+      <c r="C170" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E170" t="s">
+        <v>13</v>
+      </c>
+      <c r="F170" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="171" customFormat="1" spans="1:6">
+      <c r="A171" t="s">
         <v>333</v>
       </c>
-      <c r="C163" s="4">
-        <v>3</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E163" t="s">
-        <v>10</v>
-      </c>
-      <c r="F163" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6">
-      <c r="A164" t="s">
+      <c r="B171" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="B164" s="3" t="s">
+      <c r="C171" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E171" t="s">
+        <v>13</v>
+      </c>
+      <c r="F171" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="172" customFormat="1" spans="1:6">
+      <c r="A172" t="s">
         <v>335</v>
       </c>
-      <c r="C164" s="4">
-        <v>3</v>
-      </c>
-      <c r="D164" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E164" t="s">
-        <v>10</v>
-      </c>
-      <c r="F164" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6">
-      <c r="A165" t="s">
+      <c r="B172" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="B165" s="3" t="s">
+      <c r="C172" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E172" t="s">
+        <v>13</v>
+      </c>
+      <c r="F172" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="173" customFormat="1" spans="1:6">
+      <c r="A173" t="s">
+        <v>168</v>
+      </c>
+      <c r="B173" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="C165" s="4">
-        <v>3</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E165" t="s">
-        <v>10</v>
-      </c>
-      <c r="F165" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6">
-      <c r="A166" t="s">
+      <c r="C173" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E173" t="s">
+        <v>13</v>
+      </c>
+      <c r="F173" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="174" customFormat="1" spans="1:6">
+      <c r="A174" t="s">
         <v>338</v>
       </c>
-      <c r="B166" s="3" t="s">
+      <c r="B174" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="C166" s="4">
-        <v>3</v>
-      </c>
-      <c r="D166" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E166" t="s">
-        <v>10</v>
-      </c>
-      <c r="F166" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6">
-      <c r="A167" t="s">
+      <c r="C174" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D174" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E174" t="s">
+        <v>13</v>
+      </c>
+      <c r="F174" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="175" customFormat="1" spans="1:6">
+      <c r="A175" t="s">
         <v>340</v>
       </c>
-      <c r="B167" s="3" t="s">
+      <c r="B175" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="C167" s="4">
-        <v>3</v>
-      </c>
-      <c r="D167" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E167" t="s">
-        <v>10</v>
-      </c>
-      <c r="F167" s="1" t="s">
-        <v>11</v>
+      <c r="C175" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D175" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E175" t="s">
+        <v>13</v>
+      </c>
+      <c r="F175" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="176" customFormat="1" spans="1:6">
+      <c r="A176" t="s">
+        <v>310</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C176" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D176" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E176" t="s">
+        <v>13</v>
+      </c>
+      <c r="F176" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="177" customFormat="1" spans="1:6">
+      <c r="A177" t="s">
+        <v>343</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C177" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D177" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E177" t="s">
+        <v>13</v>
+      </c>
+      <c r="F177" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="178" customFormat="1" spans="1:6">
+      <c r="A178" t="s">
+        <v>345</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="C178" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E178" t="s">
+        <v>13</v>
+      </c>
+      <c r="F178" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="179" customFormat="1" spans="1:6">
+      <c r="A179" t="s">
+        <v>347</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="C179" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D179" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E179" t="s">
+        <v>13</v>
+      </c>
+      <c r="F179" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="180" customFormat="1" spans="1:6">
+      <c r="A180" t="s">
+        <v>349</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C180" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E180" t="s">
+        <v>13</v>
+      </c>
+      <c r="F180" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="181" customFormat="1" spans="1:6">
+      <c r="A181" t="s">
+        <v>351</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C181" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E181" t="s">
+        <v>13</v>
+      </c>
+      <c r="F181" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="182" customFormat="1" spans="1:6">
+      <c r="A182" t="s">
+        <v>353</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="C182" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E182" t="s">
+        <v>13</v>
+      </c>
+      <c r="F182" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="183" customFormat="1" spans="1:6">
+      <c r="A183" t="s">
+        <v>355</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="C183" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E183" t="s">
+        <v>13</v>
+      </c>
+      <c r="F183" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="184" customFormat="1" spans="1:6">
+      <c r="A184" t="s">
+        <v>357</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="C184" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E184" t="s">
+        <v>13</v>
+      </c>
+      <c r="F184" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="185" customFormat="1" spans="1:6">
+      <c r="A185" t="s">
+        <v>359</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="C185" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D185" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E185" t="s">
+        <v>13</v>
+      </c>
+      <c r="F185" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="186" customFormat="1" spans="1:6">
+      <c r="A186" t="s">
+        <v>361</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="C186" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D186" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E186" t="s">
+        <v>13</v>
+      </c>
+      <c r="F186" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="187" customFormat="1" spans="1:6">
+      <c r="A187" t="s">
+        <v>363</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="C187" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E187" t="s">
+        <v>13</v>
+      </c>
+      <c r="F187" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="188" customFormat="1" spans="1:6">
+      <c r="A188" t="s">
+        <v>365</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="C188" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D188" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E188" t="s">
+        <v>13</v>
+      </c>
+      <c r="F188" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="189" customFormat="1" spans="1:6">
+      <c r="A189" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="C189" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E189" t="s">
+        <v>13</v>
+      </c>
+      <c r="F189" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="190" customFormat="1" spans="1:6">
+      <c r="A190" t="s">
+        <v>58</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="C190" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E190" t="s">
+        <v>13</v>
+      </c>
+      <c r="F190" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="191" customFormat="1" spans="1:6">
+      <c r="A191" t="s">
+        <v>370</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C191" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D191" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E191" t="s">
+        <v>13</v>
+      </c>
+      <c r="F191" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="192" customFormat="1" spans="1:6">
+      <c r="A192" t="s">
+        <v>372</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C192" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D192" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E192" t="s">
+        <v>13</v>
+      </c>
+      <c r="F192" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F165" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
-  <conditionalFormatting sqref="B$1:B$1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
